--- a/data/LORRY DAILY PLANNING.xlsx
+++ b/data/LORRY DAILY PLANNING.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366B4584-4FF7-4A02-924D-40B6E3AE5CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136690E0-A7BD-46F4-9879-82C699D16ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
   </bookViews>
   <sheets>
     <sheet name="VIVIAN" sheetId="3" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="158">
   <si>
     <t>NO</t>
   </si>
@@ -502,6 +502,9 @@
     <t>MON</t>
   </si>
   <si>
+    <t>TEUS</t>
+  </si>
+  <si>
     <t>WED</t>
   </si>
   <si>
@@ -517,14 +520,14 @@
     <t>SUN</t>
   </si>
   <si>
-    <t>TUE</t>
+    <t>NAME</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,13 +541,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -604,8 +600,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -628,6 +647,36 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -709,101 +758,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -813,6 +854,49 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1176,330 +1260,330 @@
   <dimension ref="A2:K16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="16" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="15" style="16" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="38.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="26.5546875" style="16" customWidth="1"/>
-    <col min="10" max="10" width="44.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="42" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="16"/>
+    <col min="1" max="1" width="10.6640625" style="12" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="15" style="12" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" style="12" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="42" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="17" customFormat="1" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:11" s="13" customFormat="1" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20">
+    <row r="3" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="11">
+      <c r="C3" s="16"/>
+      <c r="D3" s="7">
         <v>13377</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20">
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16">
         <f>D3-F3</f>
         <v>13377</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="28">
+      <c r="I3" s="16"/>
+      <c r="J3" s="24">
         <f>F3/D3*100%</f>
         <v>0</v>
       </c>
-      <c r="K3" s="29"/>
-    </row>
-    <row r="4" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20">
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="7">
         <v>14164.5</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16">
         <f t="shared" ref="G4:G12" si="0">D4-F4</f>
         <v>14164.5</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="28">
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="24">
         <f t="shared" ref="J4:J12" si="1">F4/D4*100%</f>
         <v>0</v>
       </c>
-      <c r="K4" s="20"/>
-    </row>
-    <row r="5" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20">
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="7">
         <v>13723.5</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16">
         <f t="shared" si="0"/>
         <v>13723.5</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="28">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K5" s="20"/>
-    </row>
-    <row r="6" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="20">
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="7">
         <v>10027.5</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20">
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16">
         <f>D6-F6</f>
         <v>10027.5</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="28">
+      <c r="I6" s="16"/>
+      <c r="J6" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="29"/>
-    </row>
-    <row r="7" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="20">
+      <c r="K6" s="25"/>
+    </row>
+    <row r="7" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16">
         <v>5</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="7">
         <v>10384.5</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20">
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16">
         <f t="shared" si="0"/>
         <v>10384.5</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="28">
+      <c r="I7" s="16"/>
+      <c r="J7" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="29"/>
-    </row>
-    <row r="8" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" spans="1:11" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <v>4620</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19">
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15">
         <f t="shared" si="0"/>
         <v>4620</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="31">
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20">
+      <c r="K8" s="28"/>
+    </row>
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="7">
         <v>4368</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20">
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16">
         <f>D6-F9</f>
         <v>10027.5</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="28">
+      <c r="I9" s="16"/>
+      <c r="J9" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K9" s="29"/>
-    </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20">
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="16">
         <v>8</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="7">
         <v>4200</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20">
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="28">
+      <c r="I10" s="16"/>
+      <c r="J10" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20">
+      <c r="K10" s="25"/>
+    </row>
+    <row r="11" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="7">
         <v>1144.5</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20">
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16">
         <f t="shared" si="0"/>
         <v>1144.5</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="28">
+      <c r="I11" s="16"/>
+      <c r="J11" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20">
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16">
         <v>10</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="28" t="e">
+      <c r="H12" s="18"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K12" s="29"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="20" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1513,435 +1597,435 @@
   <dimension ref="A2:K16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="16" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17" style="16" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="38.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="33.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.88671875" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="16"/>
+    <col min="1" max="1" width="10.6640625" style="12" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="17" style="12" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="33.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="17" customFormat="1" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+    <row r="2" spans="1:11" s="13" customFormat="1" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="20">
+    <row r="3" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="16">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="17">
         <v>21000</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="16">
         <v>4</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="16">
         <v>21110</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="16">
         <f>D3-F3</f>
         <v>-110</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="24">
         <f>F3/D3*100%</f>
         <v>1.0052380952380953</v>
       </c>
-      <c r="K3" s="29"/>
-    </row>
-    <row r="4" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="33">
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="29">
         <v>2</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="30">
         <v>14311.5</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33">
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29">
         <f t="shared" ref="G4:G13" si="0">D4-F4</f>
         <v>14311.5</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="36">
+      <c r="H4" s="31"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="32">
         <f t="shared" ref="J4:J7" si="1">F4/D4*100%</f>
         <v>0</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="29" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="20">
+    <row r="5" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="16">
         <v>3</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="17">
         <v>14689.5</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="16">
         <v>4</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="16">
         <v>14156</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="16">
         <f t="shared" si="0"/>
         <v>533.5</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="24">
         <f t="shared" si="1"/>
         <v>0.96368154123693794</v>
       </c>
-      <c r="K5" s="20"/>
-    </row>
-    <row r="6" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="20">
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="16">
         <v>4</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="17">
         <v>14542.5</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <v>7</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="16">
         <v>13962</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="16">
         <f t="shared" si="0"/>
         <v>580.5</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="24">
         <f t="shared" si="1"/>
         <v>0.96008251676121714</v>
       </c>
-      <c r="K6" s="29"/>
-    </row>
-    <row r="7" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="20">
+      <c r="K6" s="25"/>
+    </row>
+    <row r="7" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="16">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="17">
         <v>13251</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="16">
         <v>4</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="16">
         <v>14610</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="16">
         <f t="shared" si="0"/>
         <v>-1359</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="24">
         <f t="shared" si="1"/>
         <v>1.1025582974869821</v>
       </c>
-      <c r="K7" s="29"/>
-    </row>
-    <row r="8" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19">
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" spans="1:11" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="17">
         <v>10762.5</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="15">
         <v>15</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="15">
         <v>12479</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="16">
         <f t="shared" si="0"/>
         <v>-1716.5</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="27">
         <f t="shared" ref="J8:J13" si="2">F8/D8*100%</f>
         <v>1.1594889663182346</v>
       </c>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="20">
+      <c r="K8" s="28"/>
+    </row>
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="16">
         <v>7</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="17">
         <v>4200</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="16">
         <v>5</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="16">
         <v>5440</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="16">
         <f t="shared" si="0"/>
         <v>-1240</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="24">
         <f t="shared" si="2"/>
         <v>1.2952380952380953</v>
       </c>
-      <c r="K9" s="29"/>
-    </row>
-    <row r="10" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20">
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="16">
         <v>8</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="17">
         <v>4200</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="16">
         <v>7</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="16">
         <v>5155</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="16">
         <f t="shared" si="0"/>
         <v>-955</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="24">
         <f t="shared" si="2"/>
         <v>1.2273809523809525</v>
       </c>
-      <c r="K10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20">
+      <c r="K10" s="25"/>
+    </row>
+    <row r="11" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="16">
         <v>9</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="16">
         <v>1113</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="16">
         <v>3</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="16">
         <v>1181</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="16">
         <f t="shared" si="0"/>
         <v>-68</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="24">
         <f t="shared" si="2"/>
         <v>1.0610961365678346</v>
       </c>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" spans="1:11" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="20">
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="16">
         <v>10</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="17">
         <v>8662.5</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="16">
         <v>14</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="16">
         <v>8936</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="16">
         <f t="shared" si="0"/>
         <v>-273.5</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="24">
         <f t="shared" si="2"/>
         <v>1.0315728715728716</v>
       </c>
-      <c r="K12" s="29"/>
-    </row>
-    <row r="13" spans="1:11" s="37" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20">
+      <c r="K12" s="25"/>
+    </row>
+    <row r="13" spans="1:11" s="33" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16">
         <v>11</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="16">
         <v>4200</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="16">
         <v>6</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="16">
         <v>5559</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="16">
         <f t="shared" si="0"/>
         <v>-1359</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="24">
         <f t="shared" si="2"/>
         <v>1.3235714285714286</v>
       </c>
-      <c r="K13" s="20"/>
+      <c r="K13" s="16"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="20" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1956,581 +2040,676 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A4:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5546875" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="5"/>
+    <col min="1" max="1" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+    <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C1" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D1" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E1" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F1" s="43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="B2" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10">
+      <c r="C2" s="45">
         <v>38000</v>
       </c>
-      <c r="C7" s="10">
+      <c r="D2" s="45">
         <v>6070</v>
       </c>
-      <c r="D7" s="10">
+      <c r="E2" s="45">
         <v>20000</v>
       </c>
-      <c r="E7" s="11">
+      <c r="F2" s="46">
         <v>21000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="45">
+        <v>25000</v>
+      </c>
+      <c r="D3" s="45">
+        <v>11150</v>
+      </c>
+      <c r="E3" s="45">
+        <f t="shared" ref="E3:E27" si="0">C3-D3</f>
+        <v>13850</v>
+      </c>
+      <c r="F3" s="46">
+        <v>14542.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="10">
+      <c r="C4" s="45">
         <v>25000</v>
       </c>
-      <c r="C8" s="10">
+      <c r="D4" s="45">
         <v>11370</v>
       </c>
-      <c r="D8" s="10">
-        <f t="shared" ref="D8:D16" si="0">B8-C8</f>
+      <c r="E4" s="45">
+        <f t="shared" si="0"/>
         <v>13630</v>
       </c>
-      <c r="E8" s="11">
+      <c r="F4" s="46">
         <v>14311.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10">
+      <c r="C5" s="45">
         <v>25000</v>
       </c>
-      <c r="C9" s="10">
+      <c r="D5" s="45">
         <v>11010</v>
       </c>
-      <c r="D9" s="10">
+      <c r="E5" s="45">
         <f t="shared" si="0"/>
         <v>13990</v>
       </c>
-      <c r="E9" s="11">
+      <c r="F5" s="46">
         <v>14689.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="10">
-        <v>25000</v>
-      </c>
-      <c r="C10" s="10">
-        <v>11150</v>
-      </c>
-      <c r="D10" s="10">
-        <f t="shared" si="0"/>
-        <v>13850</v>
-      </c>
-      <c r="E10" s="11">
-        <v>14542.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="10">
+      <c r="C6" s="45">
         <v>24000</v>
       </c>
-      <c r="C11" s="10">
+      <c r="D6" s="45">
         <v>11380</v>
       </c>
-      <c r="D11" s="10">
+      <c r="E6" s="45">
         <f t="shared" si="0"/>
         <v>12620</v>
       </c>
-      <c r="E11" s="11">
+      <c r="F6" s="46">
         <v>13251</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="10">
+      <c r="C7" s="45">
         <v>19000</v>
       </c>
-      <c r="C12" s="10">
+      <c r="D7" s="45">
         <v>8750</v>
       </c>
-      <c r="D12" s="10">
+      <c r="E7" s="45">
         <f t="shared" si="0"/>
         <v>10250</v>
       </c>
-      <c r="E12" s="11">
+      <c r="F7" s="46">
         <v>10762.5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="10">
+      <c r="C8" s="45">
         <v>7500</v>
       </c>
-      <c r="C13" s="10">
+      <c r="D8" s="45">
         <v>4170</v>
       </c>
-      <c r="D13" s="10">
+      <c r="E8" s="45">
         <f t="shared" si="0"/>
         <v>3330</v>
       </c>
-      <c r="E13" s="11">
+      <c r="F8" s="46">
         <v>4200</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="10">
+      <c r="C9" s="45">
         <v>5000</v>
       </c>
-      <c r="C14" s="10">
+      <c r="D9" s="45">
         <v>3280</v>
       </c>
-      <c r="D14" s="10">
+      <c r="E9" s="45">
         <f t="shared" si="0"/>
         <v>1720</v>
       </c>
-      <c r="E14" s="11">
+      <c r="F9" s="46">
         <v>4200</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="10">
+      <c r="C10" s="45">
         <v>5000</v>
       </c>
-      <c r="C15" s="10">
+      <c r="D10" s="45">
         <v>3000</v>
       </c>
-      <c r="D15" s="10">
+      <c r="E10" s="45">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="E15" s="11">
+      <c r="F10" s="46">
         <v>4200</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="10">
+      <c r="C11" s="45">
         <v>2800</v>
       </c>
-      <c r="C16" s="10">
+      <c r="D11" s="45">
         <v>1740</v>
       </c>
-      <c r="D16" s="10">
+      <c r="E11" s="45">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
-      <c r="E16" s="11">
+      <c r="F11" s="46">
         <v>1113</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="48">
+        <v>7700</v>
+      </c>
+      <c r="D12" s="48">
+        <v>3700</v>
+      </c>
+      <c r="E12" s="48">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="F12" s="49">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="48">
+        <v>7500</v>
+      </c>
+      <c r="D13" s="48">
+        <v>3910</v>
+      </c>
+      <c r="E13" s="48">
+        <f t="shared" si="0"/>
+        <v>3590</v>
+      </c>
+      <c r="F13" s="49">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="48">
+        <v>7500</v>
+      </c>
+      <c r="D14" s="48">
+        <v>3470</v>
+      </c>
+      <c r="E14" s="48">
+        <f t="shared" si="0"/>
+        <v>4030</v>
+      </c>
+      <c r="F14" s="49">
+        <v>4231.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="51">
+        <v>13500</v>
+      </c>
+      <c r="D15" s="51">
+        <v>5410</v>
+      </c>
+      <c r="E15" s="51">
+        <f t="shared" si="0"/>
+        <v>8090</v>
+      </c>
+      <c r="F15" s="52">
+        <v>8494.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="54">
+        <v>24000</v>
+      </c>
+      <c r="D16" s="54">
+        <v>11320</v>
+      </c>
+      <c r="E16" s="54">
+        <f t="shared" si="0"/>
+        <v>12680</v>
+      </c>
+      <c r="F16" s="55">
+        <v>13314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="54">
+        <v>14200</v>
+      </c>
+      <c r="D17" s="54">
+        <v>5950</v>
+      </c>
+      <c r="E17" s="54">
+        <f t="shared" si="0"/>
+        <v>8250</v>
+      </c>
+      <c r="F17" s="55">
+        <v>8662.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="54">
+        <v>5000</v>
+      </c>
+      <c r="D18" s="54">
+        <v>3380</v>
+      </c>
+      <c r="E18" s="54">
+        <f t="shared" si="0"/>
+        <v>1620</v>
+      </c>
+      <c r="F18" s="55">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="B19" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="57">
+        <v>25000</v>
+      </c>
+      <c r="D19" s="57">
+        <v>11510</v>
+      </c>
+      <c r="E19" s="57">
+        <f t="shared" si="0"/>
+        <v>13490</v>
+      </c>
+      <c r="F19" s="58">
+        <v>14164.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="57">
+        <v>24000</v>
+      </c>
+      <c r="D20" s="57">
+        <v>10930</v>
+      </c>
+      <c r="E20" s="57">
+        <f t="shared" si="0"/>
+        <v>13070</v>
+      </c>
+      <c r="F20" s="58">
+        <v>13723.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="10">
+      <c r="C21" s="57">
         <v>24000</v>
       </c>
-      <c r="C19" s="10">
+      <c r="D21" s="57">
         <v>11260</v>
       </c>
-      <c r="D19" s="10">
-        <f>B19-C19</f>
+      <c r="E21" s="57">
+        <f t="shared" si="0"/>
         <v>12740</v>
       </c>
-      <c r="E19" s="11">
+      <c r="F21" s="58">
         <v>13377</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="10">
-        <v>25000</v>
-      </c>
-      <c r="C20" s="10">
-        <v>11510</v>
-      </c>
-      <c r="D20" s="10">
-        <f t="shared" ref="D20:D27" si="1">B20-C20</f>
-        <v>13490</v>
-      </c>
-      <c r="E20" s="11">
-        <v>14164.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="10">
-        <v>24000</v>
-      </c>
-      <c r="C21" s="10">
-        <v>10930</v>
-      </c>
-      <c r="D21" s="10">
-        <f t="shared" si="1"/>
-        <v>13070</v>
-      </c>
-      <c r="E21" s="11">
-        <v>13723.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="10">
+      <c r="C22" s="57">
         <v>19000</v>
       </c>
-      <c r="C22" s="10">
+      <c r="D22" s="57">
         <v>9450</v>
       </c>
-      <c r="D22" s="10">
-        <f t="shared" si="1"/>
+      <c r="E22" s="57">
+        <f t="shared" si="0"/>
         <v>9550</v>
       </c>
-      <c r="E22" s="11">
+      <c r="F22" s="58">
         <v>10027.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="10">
+      <c r="C23" s="57">
         <v>19000</v>
       </c>
-      <c r="C23" s="10">
+      <c r="D23" s="57">
         <v>9110</v>
       </c>
-      <c r="D23" s="10">
-        <f t="shared" si="1"/>
+      <c r="E23" s="57">
+        <f t="shared" si="0"/>
         <v>9890</v>
       </c>
-      <c r="E23" s="11">
+      <c r="F23" s="58">
         <v>10384.5</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="10">
+      <c r="C24" s="57">
         <v>8500</v>
       </c>
-      <c r="C24" s="10">
+      <c r="D24" s="57">
         <v>4100</v>
       </c>
-      <c r="D24" s="10">
-        <f t="shared" si="1"/>
+      <c r="E24" s="57">
+        <f t="shared" si="0"/>
         <v>4400</v>
       </c>
-      <c r="E24" s="11">
+      <c r="F24" s="58">
         <v>4620</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="10">
+      <c r="C25" s="57">
         <v>7500</v>
       </c>
-      <c r="C25" s="10">
+      <c r="D25" s="57">
         <v>3340</v>
       </c>
-      <c r="D25" s="10">
-        <f t="shared" si="1"/>
+      <c r="E25" s="57">
+        <f t="shared" si="0"/>
         <v>4160</v>
       </c>
-      <c r="E25" s="11">
+      <c r="F25" s="58">
         <v>4368</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="10">
+      <c r="C26" s="57">
         <v>5000</v>
       </c>
-      <c r="C26" s="10">
+      <c r="D26" s="57">
         <v>3530</v>
       </c>
-      <c r="D26" s="10">
-        <f t="shared" si="1"/>
+      <c r="E26" s="57">
+        <f t="shared" si="0"/>
         <v>1470</v>
       </c>
-      <c r="E26" s="11">
+      <c r="F26" s="58">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="10">
+      <c r="C27" s="59">
         <v>2800</v>
       </c>
-      <c r="C27" s="10">
+      <c r="D27" s="57">
         <v>1710</v>
       </c>
-      <c r="D27" s="10">
-        <f t="shared" si="1"/>
+      <c r="E27" s="57">
+        <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="E27" s="11">
+      <c r="F27" s="58">
         <v>1144.5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="12"/>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="12"/>
-    </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="10">
-        <v>24000</v>
-      </c>
-      <c r="C30" s="10">
-        <v>11320</v>
-      </c>
-      <c r="D30" s="10">
-        <f t="shared" ref="D30:D35" si="2">B30-C30</f>
-        <v>12680</v>
-      </c>
-      <c r="E30" s="11">
-        <v>13314</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="10">
-        <v>14200</v>
-      </c>
-      <c r="C31" s="10">
-        <v>5950</v>
-      </c>
-      <c r="D31" s="10">
-        <f t="shared" si="2"/>
-        <v>8250</v>
-      </c>
-      <c r="E31" s="11">
-        <v>8662.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="10">
-        <v>5000</v>
-      </c>
-      <c r="C32" s="10">
-        <v>3380</v>
-      </c>
-      <c r="D32" s="10">
-        <f t="shared" si="2"/>
-        <v>1620</v>
-      </c>
-      <c r="E32" s="11">
-        <v>4200</v>
-      </c>
+    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="12"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="12"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="8"/>
     </row>
     <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="10">
-        <v>13500</v>
-      </c>
-      <c r="C35" s="10">
-        <v>5410</v>
-      </c>
-      <c r="D35" s="10">
-        <f t="shared" si="2"/>
-        <v>8090</v>
-      </c>
-      <c r="E35" s="11">
-        <v>8494.5</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="12"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="8"/>
     </row>
     <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="12"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="10">
-        <v>7500</v>
-      </c>
-      <c r="C38" s="10">
-        <v>3470</v>
-      </c>
-      <c r="D38" s="10">
-        <f t="shared" ref="D38:D39" si="3">B38-C38</f>
-        <v>4030</v>
-      </c>
-      <c r="E38" s="11">
-        <v>4231.5</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="10">
-        <v>7500</v>
-      </c>
-      <c r="C39" s="10">
-        <v>3910</v>
-      </c>
-      <c r="D39" s="10">
-        <f t="shared" si="3"/>
-        <v>3590</v>
-      </c>
-      <c r="E39" s="11">
-        <v>4200</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="7"/>
     </row>
     <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="14">
-        <v>7700</v>
-      </c>
-      <c r="C40" s="10">
-        <v>3700</v>
-      </c>
-      <c r="D40" s="10">
-        <f>B40-C40</f>
-        <v>4000</v>
-      </c>
-      <c r="E40" s="11">
-        <v>4200</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="7"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="15"/>
+      <c r="E41" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3164,24 +3343,24 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="39">
+      <c r="A27" s="35">
         <v>68</v>
       </c>
-      <c r="B27" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="38" t="s">
+      <c r="B27" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="34" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="41">
+      <c r="A28" s="37">
         <v>90</v>
       </c>
-      <c r="B28" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="43" t="s">
+      <c r="B28" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="39" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4411,41 +4590,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
       <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" t="s">
         <v>156</v>
       </c>
-      <c r="C2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" t="s">
-        <v>155</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="41" t="s">
         <v>106</v>
       </c>
       <c r="B3" t="s">
@@ -4465,7 +4644,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="41" t="s">
         <v>107</v>
       </c>
       <c r="B4" t="s">
@@ -4485,7 +4664,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="41" t="s">
         <v>108</v>
       </c>
       <c r="B5" t="s">
@@ -4502,7 +4681,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="41" t="s">
         <v>111</v>
       </c>
       <c r="B6" t="s">
@@ -4519,7 +4698,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="41" t="s">
         <v>112</v>
       </c>
       <c r="B7" t="s">
@@ -4536,7 +4715,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="41" t="s">
         <v>115</v>
       </c>
       <c r="B8" t="s">
@@ -4553,7 +4732,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="41" t="s">
         <v>116</v>
       </c>
       <c r="B9" t="s">
@@ -4567,7 +4746,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="41" t="s">
         <v>117</v>
       </c>
       <c r="B10" t="s">
@@ -4581,7 +4760,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="41" t="s">
         <v>119</v>
       </c>
       <c r="B11" t="s">
@@ -4595,7 +4774,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="41" t="s">
         <v>120</v>
       </c>
       <c r="B12" t="s">
@@ -4603,7 +4782,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="41" t="s">
         <v>77</v>
       </c>
       <c r="B13" t="s">
@@ -4611,7 +4790,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="41" t="s">
         <v>118</v>
       </c>
       <c r="B14" t="s">
@@ -4650,37 +4829,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>150</v>
       </c>
       <c r="B2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" t="s">
         <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">

--- a/data/LORRY DAILY PLANNING.xlsx
+++ b/data/LORRY DAILY PLANNING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CEB2AF-AAD0-449E-9476-A1D9F7B9CAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9C5513-9F2B-4BBF-95C3-33CE2B0E37E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="526">
   <si>
     <t>NO</t>
   </si>
@@ -1626,6 +1626,9 @@
   </si>
   <si>
     <t>Bakelalan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -3512,14 +3515,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB923D5B-1288-4E4B-A42D-1967DA205059}">
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:F352"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>161</v>
       </c>
@@ -3527,7 +3530,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
         <v>163</v>
       </c>
@@ -3535,7 +3538,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52" t="s">
         <v>163</v>
       </c>
@@ -3543,7 +3546,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50" t="s">
         <v>163</v>
       </c>
@@ -3551,7 +3554,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="52" t="s">
         <v>163</v>
       </c>
@@ -3559,7 +3562,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50" t="s">
         <v>163</v>
       </c>
@@ -3567,7 +3570,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="52" t="s">
         <v>163</v>
       </c>
@@ -3575,7 +3578,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
         <v>163</v>
       </c>
@@ -3583,7 +3586,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52" t="s">
         <v>163</v>
       </c>
@@ -3591,7 +3594,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50" t="s">
         <v>163</v>
       </c>
@@ -3599,7 +3602,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="52" t="s">
         <v>163</v>
       </c>
@@ -3607,7 +3610,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
         <v>163</v>
       </c>
@@ -3615,7 +3618,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="52" t="s">
         <v>163</v>
       </c>
@@ -3623,15 +3626,18 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50" t="s">
         <v>163</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="52" t="s">
         <v>163</v>
       </c>
@@ -3639,7 +3645,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50" t="s">
         <v>163</v>
       </c>

--- a/data/LORRY DAILY PLANNING.xlsx
+++ b/data/LORRY DAILY PLANNING.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CB7717-6537-4BC5-9C99-A54C2B20752F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{48CB7717-6537-4BC5-9C99-A54C2B20752F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACFA8ED7-0D89-4BBB-B357-B3CE536EF5BD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
   </bookViews>
   <sheets>
     <sheet name="VIVIAN" sheetId="3" r:id="rId1"/>
@@ -1650,7 +1650,7 @@
     <t>VAN</t>
   </si>
   <si>
-    <t>TEUS,THUS,SAT</t>
+    <t>TUE,THUS,SAT</t>
   </si>
   <si>
     <t>PM ONLY</t>
@@ -1668,7 +1668,7 @@
     <t>BELOW 10 TON</t>
   </si>
   <si>
-    <t>TEUS,FRI</t>
+    <t>TUE,FRI</t>
   </si>
   <si>
     <t>EARLY MORNING</t>
@@ -1695,7 +1695,7 @@
     <t>ANY SIZE</t>
   </si>
   <si>
-    <t>EVERY TEUS</t>
+    <t>EVERY TUE</t>
   </si>
   <si>
     <t>10AM - 7PM</t>
@@ -1723,7 +1723,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1953,7 +1953,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2092,6 +2092,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2448,22 +2449,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D39D926-E7A0-4D94-A6B9-A8D9A8B3E680}">
   <dimension ref="A2:K16"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="24.6"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="15" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="38.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="44.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="38.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="44.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="42" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="2"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="68.400000000000006" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="68.45">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -2498,7 +2499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -2525,7 +2526,7 @@
       </c>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -2552,7 +2553,7 @@
       </c>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -2579,7 +2580,7 @@
       </c>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -2608,7 +2609,7 @@
       </c>
       <c r="K6" s="15"/>
     </row>
-    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -2637,7 +2638,7 @@
       </c>
       <c r="K7" s="15"/>
     </row>
-    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -2664,7 +2665,7 @@
       </c>
       <c r="K8" s="18"/>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -2693,7 +2694,7 @@
       </c>
       <c r="K9" s="15"/>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -2722,7 +2723,7 @@
       </c>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -2751,7 +2752,7 @@
       </c>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -2772,7 +2773,7 @@
       </c>
       <c r="K12" s="15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11">
       <c r="I16" s="10" t="s">
         <v>12</v>
       </c>
@@ -2785,246 +2786,258 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A8250D7-37BD-4D62-A9F5-193381FD3734}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="54" t="s">
         <v>445</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="53" t="s">
         <v>519</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="53" t="s">
         <v>520</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="53" t="s">
         <v>521</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="53" t="s">
         <v>522</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="53" t="s">
         <v>523</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="53" t="s">
         <v>524</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="53" t="s">
         <v>449</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="53" t="s">
         <v>499</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="53" t="s">
         <v>449</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="53" t="s">
         <v>506</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="53" t="s">
         <v>449</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="53" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G3" s="53"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="53" t="s">
         <v>450</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="53" t="s">
         <v>450</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="53" t="s">
         <v>507</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="53" t="s">
         <v>450</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="53" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="G4" s="53"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="53" t="s">
         <v>451</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="53" t="s">
         <v>464</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="53" t="s">
         <v>451</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="53" t="s">
         <v>508</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="53" t="s">
         <v>451</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="53" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="G5" s="53"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="53" t="s">
         <v>452</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="53" t="s">
         <v>465</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="53" t="s">
         <v>452</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="53" t="s">
         <v>509</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="53" t="s">
         <v>452</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="53" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="G6" s="53"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="53" t="s">
         <v>453</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="53" t="s">
         <v>512</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="53" t="s">
         <v>453</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="53" t="s">
         <v>455</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="53" t="s">
         <v>453</v>
       </c>
       <c r="F7" s="24" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="G7" s="53"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="53" t="s">
         <v>506</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="53" t="s">
         <v>506</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="53" t="s">
         <v>466</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="53" t="s">
         <v>499</v>
       </c>
       <c r="F8" s="24" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="G8" s="53"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="53" t="s">
         <v>507</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="53" t="s">
         <v>507</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="53" t="s">
         <v>467</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="53" t="s">
         <v>506</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="G9" s="53"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="53" t="s">
         <v>508</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53" t="s">
         <v>508</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="53" t="s">
         <v>513</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="53" t="s">
         <v>507</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="G10" s="53"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="53" t="s">
         <v>509</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>499</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="53" t="s">
         <v>454</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>499</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="53" t="s">
         <v>508</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="G11" s="53"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="53" t="s">
         <v>455</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="53" t="s">
         <v>488</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="53" t="s">
         <v>510</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="G12" s="53"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="53" t="s">
         <v>466</v>
       </c>
       <c r="B13" s="24" t="s">
@@ -3036,15 +3049,16 @@
       <c r="D13" s="24" t="s">
         <v>501</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="53" t="s">
         <v>465</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="G13" s="53"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="53" t="s">
         <v>467</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3056,12 +3070,14 @@
       <c r="D14" s="24" t="s">
         <v>502</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="53" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="53" t="s">
         <v>513</v>
       </c>
       <c r="B15" s="24" t="s">
@@ -3076,8 +3092,10 @@
       <c r="E15" s="24" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="24" t="s">
         <v>499</v>
       </c>
@@ -3093,8 +3111,10 @@
       <c r="E16" s="24" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="24" t="s">
         <v>500</v>
       </c>
@@ -3111,48 +3131,62 @@
         <v>501</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="24" t="s">
         <v>501</v>
       </c>
+      <c r="B18" s="53"/>
       <c r="C18" s="24" t="s">
         <v>507</v>
       </c>
+      <c r="D18" s="53"/>
       <c r="E18" s="24" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="24" t="s">
         <v>502</v>
       </c>
+      <c r="B19" s="53"/>
       <c r="C19" s="24" t="s">
         <v>508</v>
       </c>
+      <c r="D19" s="53"/>
       <c r="E19" s="24" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="24" t="s">
         <v>506</v>
       </c>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
       <c r="E20" s="24" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="24" t="s">
         <v>507</v>
       </c>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
       <c r="E21" s="24" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="24" t="s">
         <v>508</v>
       </c>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3165,125 +3199,161 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D2F47F-936F-424A-96FD-34C50C33A88E}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53" t="s">
         <v>527</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="53"/>
+      <c r="E1" s="53" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="53" t="s">
         <v>529</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53" t="s">
         <v>530</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="53" t="s">
         <v>532</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="53" t="s">
         <v>533</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="53"/>
+      <c r="E3" s="53" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="53" t="s">
         <v>535</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="53"/>
+      <c r="C4" s="53" t="s">
         <v>536</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="53"/>
+      <c r="E4" s="53" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="53" t="s">
         <v>538</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53" t="s">
         <v>539</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="53"/>
+      <c r="E5" s="53" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="53" t="s">
         <v>541</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53" t="s">
         <v>542</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="53"/>
+      <c r="E6" s="53" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="53" t="s">
         <v>544</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53" t="s">
         <v>545</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="53"/>
+      <c r="E7" s="53" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="53" t="s">
         <v>547</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="53" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="53" t="s">
         <v>549</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="53" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="53" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="53" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="53" t="s">
         <v>554</v>
       </c>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3293,22 +3363,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEDE0C5-2A47-4471-88E7-341CFFF617B6}">
   <dimension ref="A2:K16"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="24.6"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="17" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="38.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="33.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="41.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="2"/>
+    <col min="6" max="6" width="19.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="38.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="33.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="45.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="45.6">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -3343,7 +3413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -3378,7 +3448,7 @@
       </c>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="19">
         <v>2</v>
       </c>
@@ -3407,7 +3477,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -3436,7 +3506,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -3471,7 +3541,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -3508,7 +3578,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -3543,7 +3613,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -3578,7 +3648,7 @@
       </c>
       <c r="K9" s="15"/>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -3613,7 +3683,7 @@
       </c>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -3648,7 +3718,7 @@
       </c>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -3683,7 +3753,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -3718,7 +3788,7 @@
       </c>
       <c r="K13" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11">
       <c r="I16" s="10" t="s">
         <v>12</v>
       </c>
@@ -3732,144 +3802,207 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB923D5B-1288-4E4B-A42D-1967DA205059}">
   <dimension ref="A1:F352"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="22.15" customHeight="1">
       <c r="A1" s="48" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="48" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+    </row>
+    <row r="2" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A2" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B2" s="50" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A3" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="52" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A4" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="50" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A5" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B5" s="52" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+    </row>
+    <row r="6" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A6" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B6" s="50" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+    </row>
+    <row r="7" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A7" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B7" s="52" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A8" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B8" s="50" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A9" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B9" s="52" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+    </row>
+    <row r="10" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A10" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+    </row>
+    <row r="11" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A11" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="52" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A12" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="50" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+    </row>
+    <row r="13" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A13" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B13" s="52" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+    </row>
+    <row r="14" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A14" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B14" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="F14" t="s">
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A15" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="52" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.899999999999999" customHeight="1">
       <c r="A16" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B16" s="50" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+    </row>
+    <row r="17" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A17" s="51" t="s">
         <v>65</v>
       </c>
@@ -3877,7 +4010,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A18" s="49" t="s">
         <v>65</v>
       </c>
@@ -3885,7 +4018,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A19" s="51" t="s">
         <v>65</v>
       </c>
@@ -3893,7 +4026,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A20" s="49" t="s">
         <v>65</v>
       </c>
@@ -3901,7 +4034,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A21" s="51" t="s">
         <v>65</v>
       </c>
@@ -3909,7 +4042,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A22" s="49" t="s">
         <v>65</v>
       </c>
@@ -3917,7 +4050,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A23" s="51" t="s">
         <v>65</v>
       </c>
@@ -3925,7 +4058,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A24" s="49" t="s">
         <v>65</v>
       </c>
@@ -3933,7 +4066,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A25" s="51" t="s">
         <v>65</v>
       </c>
@@ -3941,7 +4074,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A26" s="49" t="s">
         <v>65</v>
       </c>
@@ -3949,7 +4082,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A27" s="51" t="s">
         <v>65</v>
       </c>
@@ -3957,7 +4090,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A28" s="49" t="s">
         <v>65</v>
       </c>
@@ -3965,7 +4098,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A29" s="51" t="s">
         <v>65</v>
       </c>
@@ -3973,7 +4106,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A30" s="49" t="s">
         <v>65</v>
       </c>
@@ -3981,7 +4114,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A31" s="51" t="s">
         <v>65</v>
       </c>
@@ -3989,7 +4122,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A32" s="49" t="s">
         <v>97</v>
       </c>
@@ -3997,7 +4130,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A33" s="51" t="s">
         <v>97</v>
       </c>
@@ -4005,7 +4138,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A34" s="49" t="s">
         <v>97</v>
       </c>
@@ -4013,7 +4146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A35" s="51" t="s">
         <v>97</v>
       </c>
@@ -4021,7 +4154,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A36" s="49" t="s">
         <v>97</v>
       </c>
@@ -4029,7 +4162,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A37" s="51" t="s">
         <v>97</v>
       </c>
@@ -4037,7 +4170,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A38" s="49" t="s">
         <v>97</v>
       </c>
@@ -4045,7 +4178,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A39" s="51" t="s">
         <v>97</v>
       </c>
@@ -4053,7 +4186,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A40" s="49" t="s">
         <v>97</v>
       </c>
@@ -4061,7 +4194,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A41" s="51" t="s">
         <v>97</v>
       </c>
@@ -4069,7 +4202,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A42" s="49" t="s">
         <v>97</v>
       </c>
@@ -4077,7 +4210,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A43" s="51" t="s">
         <v>97</v>
       </c>
@@ -4085,7 +4218,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A44" s="49" t="s">
         <v>97</v>
       </c>
@@ -4093,7 +4226,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A45" s="51" t="s">
         <v>97</v>
       </c>
@@ -4101,7 +4234,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A46" s="49" t="s">
         <v>97</v>
       </c>
@@ -4109,7 +4242,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A47" s="51" t="s">
         <v>97</v>
       </c>
@@ -4117,7 +4250,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A48" s="49" t="s">
         <v>97</v>
       </c>
@@ -4125,7 +4258,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A49" s="51" t="s">
         <v>97</v>
       </c>
@@ -4133,7 +4266,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A50" s="49" t="s">
         <v>97</v>
       </c>
@@ -4141,7 +4274,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A51" s="51" t="s">
         <v>97</v>
       </c>
@@ -4149,7 +4282,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A52" s="49" t="s">
         <v>97</v>
       </c>
@@ -4157,7 +4290,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A53" s="51" t="s">
         <v>97</v>
       </c>
@@ -4165,7 +4298,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A54" s="49" t="s">
         <v>97</v>
       </c>
@@ -4173,7 +4306,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A55" s="51" t="s">
         <v>97</v>
       </c>
@@ -4181,7 +4314,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A56" s="49" t="s">
         <v>97</v>
       </c>
@@ -4189,7 +4322,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A57" s="51" t="s">
         <v>97</v>
       </c>
@@ -4197,7 +4330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A58" s="49" t="s">
         <v>121</v>
       </c>
@@ -4205,7 +4338,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A59" s="51" t="s">
         <v>121</v>
       </c>
@@ -4213,7 +4346,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A60" s="49" t="s">
         <v>121</v>
       </c>
@@ -4221,7 +4354,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A61" s="51" t="s">
         <v>121</v>
       </c>
@@ -4229,7 +4362,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A62" s="49" t="s">
         <v>121</v>
       </c>
@@ -4237,7 +4370,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A63" s="51" t="s">
         <v>121</v>
       </c>
@@ -4245,7 +4378,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A64" s="49" t="s">
         <v>121</v>
       </c>
@@ -4253,7 +4386,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A65" s="51" t="s">
         <v>121</v>
       </c>
@@ -4261,7 +4394,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A66" s="49" t="s">
         <v>121</v>
       </c>
@@ -4269,7 +4402,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A67" s="51" t="s">
         <v>121</v>
       </c>
@@ -4277,7 +4410,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A68" s="49" t="s">
         <v>121</v>
       </c>
@@ -4285,7 +4418,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A69" s="49" t="s">
         <v>133</v>
       </c>
@@ -4293,7 +4426,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A70" s="51" t="s">
         <v>133</v>
       </c>
@@ -4301,7 +4434,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A71" s="49" t="s">
         <v>133</v>
       </c>
@@ -4309,7 +4442,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A72" s="51" t="s">
         <v>133</v>
       </c>
@@ -4317,7 +4450,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A73" s="49" t="s">
         <v>133</v>
       </c>
@@ -4325,7 +4458,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A74" s="51" t="s">
         <v>133</v>
       </c>
@@ -4333,7 +4466,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A75" s="49" t="s">
         <v>133</v>
       </c>
@@ -4341,7 +4474,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A76" s="51" t="s">
         <v>133</v>
       </c>
@@ -4349,7 +4482,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A77" s="49" t="s">
         <v>142</v>
       </c>
@@ -4357,7 +4490,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A78" s="51" t="s">
         <v>142</v>
       </c>
@@ -4365,7 +4498,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A79" s="49" t="s">
         <v>142</v>
       </c>
@@ -4373,7 +4506,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A80" s="51" t="s">
         <v>142</v>
       </c>
@@ -4381,7 +4514,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A81" s="49" t="s">
         <v>142</v>
       </c>
@@ -4389,7 +4522,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A82" s="51" t="s">
         <v>142</v>
       </c>
@@ -4397,7 +4530,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A83" s="49" t="s">
         <v>142</v>
       </c>
@@ -4405,7 +4538,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A84" s="51" t="s">
         <v>142</v>
       </c>
@@ -4413,7 +4546,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A85" s="49" t="s">
         <v>142</v>
       </c>
@@ -4421,7 +4554,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A86" s="51" t="s">
         <v>142</v>
       </c>
@@ -4429,7 +4562,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A87" s="49" t="s">
         <v>142</v>
       </c>
@@ -4437,7 +4570,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A88" s="51" t="s">
         <v>142</v>
       </c>
@@ -4445,7 +4578,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A89" s="49" t="s">
         <v>142</v>
       </c>
@@ -4453,7 +4586,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A90" s="51" t="s">
         <v>142</v>
       </c>
@@ -4461,7 +4594,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A91" s="49" t="s">
         <v>142</v>
       </c>
@@ -4469,7 +4602,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A92" s="51" t="s">
         <v>142</v>
       </c>
@@ -4477,7 +4610,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A93" s="49" t="s">
         <v>142</v>
       </c>
@@ -4485,7 +4618,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A94" s="51" t="s">
         <v>142</v>
       </c>
@@ -4493,7 +4626,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A95" s="49" t="s">
         <v>142</v>
       </c>
@@ -4501,7 +4634,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A96" s="51" t="s">
         <v>142</v>
       </c>
@@ -4509,7 +4642,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A97" s="49" t="s">
         <v>142</v>
       </c>
@@ -4517,7 +4650,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A98" s="51" t="s">
         <v>142</v>
       </c>
@@ -4525,7 +4658,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A99" s="49" t="s">
         <v>142</v>
       </c>
@@ -4533,7 +4666,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A100" s="51" t="s">
         <v>142</v>
       </c>
@@ -4541,7 +4674,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A101" s="49" t="s">
         <v>142</v>
       </c>
@@ -4549,7 +4682,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A102" s="51" t="s">
         <v>142</v>
       </c>
@@ -4557,7 +4690,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A103" s="49" t="s">
         <v>142</v>
       </c>
@@ -4565,7 +4698,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A104" s="51" t="s">
         <v>142</v>
       </c>
@@ -4573,7 +4706,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A105" s="49" t="s">
         <v>142</v>
       </c>
@@ -4581,7 +4714,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A106" s="51" t="s">
         <v>142</v>
       </c>
@@ -4589,7 +4722,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A107" s="49" t="s">
         <v>142</v>
       </c>
@@ -4597,7 +4730,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A108" s="49" t="s">
         <v>174</v>
       </c>
@@ -4605,7 +4738,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A109" s="51" t="s">
         <v>174</v>
       </c>
@@ -4613,7 +4746,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A110" s="49" t="s">
         <v>174</v>
       </c>
@@ -4621,7 +4754,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A111" s="51" t="s">
         <v>174</v>
       </c>
@@ -4629,7 +4762,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A112" s="49" t="s">
         <v>174</v>
       </c>
@@ -4637,7 +4770,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A113" s="51" t="s">
         <v>174</v>
       </c>
@@ -4645,7 +4778,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A114" s="49" t="s">
         <v>174</v>
       </c>
@@ -4653,7 +4786,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A115" s="51" t="s">
         <v>174</v>
       </c>
@@ -4661,7 +4794,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A116" s="49" t="s">
         <v>174</v>
       </c>
@@ -4669,7 +4802,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A117" s="51" t="s">
         <v>174</v>
       </c>
@@ -4677,7 +4810,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A118" s="49" t="s">
         <v>174</v>
       </c>
@@ -4685,7 +4818,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A119" s="51" t="s">
         <v>174</v>
       </c>
@@ -4693,7 +4826,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A120" s="49" t="s">
         <v>174</v>
       </c>
@@ -4701,7 +4834,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A121" s="51" t="s">
         <v>174</v>
       </c>
@@ -4709,7 +4842,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A122" s="49" t="s">
         <v>174</v>
       </c>
@@ -4717,7 +4850,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A123" s="51" t="s">
         <v>174</v>
       </c>
@@ -4725,7 +4858,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A124" s="49" t="s">
         <v>174</v>
       </c>
@@ -4733,7 +4866,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A125" s="51" t="s">
         <v>174</v>
       </c>
@@ -4741,7 +4874,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A126" s="49" t="s">
         <v>174</v>
       </c>
@@ -4749,7 +4882,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A127" s="51" t="s">
         <v>174</v>
       </c>
@@ -4757,7 +4890,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A128" s="49" t="s">
         <v>174</v>
       </c>
@@ -4765,7 +4898,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A129" s="51" t="s">
         <v>174</v>
       </c>
@@ -4773,7 +4906,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A130" s="49" t="s">
         <v>174</v>
       </c>
@@ -4781,7 +4914,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A131" s="51" t="s">
         <v>174</v>
       </c>
@@ -4789,7 +4922,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A132" s="49" t="s">
         <v>174</v>
       </c>
@@ -4797,7 +4930,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A133" s="51" t="s">
         <v>174</v>
       </c>
@@ -4805,7 +4938,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A134" s="49" t="s">
         <v>174</v>
       </c>
@@ -4813,7 +4946,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A135" s="51" t="s">
         <v>174</v>
       </c>
@@ -4821,7 +4954,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A136" s="49" t="s">
         <v>174</v>
       </c>
@@ -4829,7 +4962,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A137" s="51" t="s">
         <v>174</v>
       </c>
@@ -4837,7 +4970,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A138" s="49" t="s">
         <v>205</v>
       </c>
@@ -4845,7 +4978,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A139" s="51" t="s">
         <v>205</v>
       </c>
@@ -4853,7 +4986,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A140" s="49" t="s">
         <v>205</v>
       </c>
@@ -4861,7 +4994,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A141" s="51" t="s">
         <v>205</v>
       </c>
@@ -4869,7 +5002,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A142" s="49" t="s">
         <v>205</v>
       </c>
@@ -4877,7 +5010,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A143" s="51" t="s">
         <v>205</v>
       </c>
@@ -4885,7 +5018,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A144" s="49" t="s">
         <v>205</v>
       </c>
@@ -4893,7 +5026,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A145" s="51" t="s">
         <v>205</v>
       </c>
@@ -4901,7 +5034,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A146" s="49" t="s">
         <v>205</v>
       </c>
@@ -4909,7 +5042,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A147" s="51" t="s">
         <v>205</v>
       </c>
@@ -4917,7 +5050,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A148" s="49" t="s">
         <v>205</v>
       </c>
@@ -4925,7 +5058,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A149" s="51" t="s">
         <v>205</v>
       </c>
@@ -4933,7 +5066,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A150" s="49" t="s">
         <v>205</v>
       </c>
@@ -4941,7 +5074,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A151" s="51" t="s">
         <v>205</v>
       </c>
@@ -4949,7 +5082,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A152" s="49" t="s">
         <v>205</v>
       </c>
@@ -4957,7 +5090,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A153" s="51" t="s">
         <v>205</v>
       </c>
@@ -4965,7 +5098,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A154" s="49" t="s">
         <v>205</v>
       </c>
@@ -4973,7 +5106,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A155" s="51" t="s">
         <v>205</v>
       </c>
@@ -4981,7 +5114,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A156" s="49" t="s">
         <v>205</v>
       </c>
@@ -4989,7 +5122,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A157" s="51" t="s">
         <v>205</v>
       </c>
@@ -4997,7 +5130,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A158" s="49" t="s">
         <v>205</v>
       </c>
@@ -5005,7 +5138,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A159" s="51" t="s">
         <v>205</v>
       </c>
@@ -5013,7 +5146,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A160" s="49" t="s">
         <v>205</v>
       </c>
@@ -5021,7 +5154,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A161" s="51" t="s">
         <v>205</v>
       </c>
@@ -5029,7 +5162,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A162" s="49" t="s">
         <v>205</v>
       </c>
@@ -5037,7 +5170,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A163" s="51" t="s">
         <v>205</v>
       </c>
@@ -5045,7 +5178,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A164" s="49" t="s">
         <v>205</v>
       </c>
@@ -5053,7 +5186,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A165" s="51" t="s">
         <v>205</v>
       </c>
@@ -5061,7 +5194,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A166" s="49" t="s">
         <v>205</v>
       </c>
@@ -5069,7 +5202,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A167" s="51" t="s">
         <v>205</v>
       </c>
@@ -5077,7 +5210,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A168" s="49" t="s">
         <v>205</v>
       </c>
@@ -5085,7 +5218,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A169" s="49" t="s">
         <v>237</v>
       </c>
@@ -5093,7 +5226,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A170" s="51" t="s">
         <v>237</v>
       </c>
@@ -5101,7 +5234,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A171" s="49" t="s">
         <v>237</v>
       </c>
@@ -5109,7 +5242,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A172" s="51" t="s">
         <v>237</v>
       </c>
@@ -5117,7 +5250,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A173" s="49" t="s">
         <v>237</v>
       </c>
@@ -5125,7 +5258,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A174" s="51" t="s">
         <v>237</v>
       </c>
@@ -5133,7 +5266,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A175" s="49" t="s">
         <v>237</v>
       </c>
@@ -5141,7 +5274,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A176" s="51" t="s">
         <v>237</v>
       </c>
@@ -5149,7 +5282,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A177" s="49" t="s">
         <v>237</v>
       </c>
@@ -5157,7 +5290,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A178" s="51" t="s">
         <v>237</v>
       </c>
@@ -5165,7 +5298,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A179" s="49" t="s">
         <v>237</v>
       </c>
@@ -5173,7 +5306,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A180" s="51" t="s">
         <v>237</v>
       </c>
@@ -5181,7 +5314,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A181" s="49" t="s">
         <v>237</v>
       </c>
@@ -5189,7 +5322,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A182" s="51" t="s">
         <v>237</v>
       </c>
@@ -5197,7 +5330,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A183" s="49" t="s">
         <v>237</v>
       </c>
@@ -5205,7 +5338,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A184" s="51" t="s">
         <v>237</v>
       </c>
@@ -5213,7 +5346,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A185" s="49" t="s">
         <v>254</v>
       </c>
@@ -5221,7 +5354,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A186" s="51" t="s">
         <v>254</v>
       </c>
@@ -5229,7 +5362,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A187" s="49" t="s">
         <v>254</v>
       </c>
@@ -5237,7 +5370,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A188" s="51" t="s">
         <v>254</v>
       </c>
@@ -5245,7 +5378,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A189" s="49" t="s">
         <v>254</v>
       </c>
@@ -5253,7 +5386,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A190" s="51" t="s">
         <v>254</v>
       </c>
@@ -5261,7 +5394,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A191" s="49" t="s">
         <v>254</v>
       </c>
@@ -5269,7 +5402,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A192" s="51" t="s">
         <v>254</v>
       </c>
@@ -5277,7 +5410,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A193" s="49" t="s">
         <v>254</v>
       </c>
@@ -5285,7 +5418,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A194" s="51" t="s">
         <v>254</v>
       </c>
@@ -5293,7 +5426,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A195" s="49" t="s">
         <v>254</v>
       </c>
@@ -5301,7 +5434,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A196" s="51" t="s">
         <v>254</v>
       </c>
@@ -5309,7 +5442,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A197" s="49" t="s">
         <v>254</v>
       </c>
@@ -5317,7 +5450,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A198" s="51" t="s">
         <v>254</v>
       </c>
@@ -5325,7 +5458,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A199" s="49" t="s">
         <v>254</v>
       </c>
@@ -5333,7 +5466,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A200" s="51" t="s">
         <v>254</v>
       </c>
@@ -5341,7 +5474,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A201" s="49" t="s">
         <v>254</v>
       </c>
@@ -5349,7 +5482,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A202" s="49" t="s">
         <v>272</v>
       </c>
@@ -5357,7 +5490,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A203" s="51" t="s">
         <v>272</v>
       </c>
@@ -5365,7 +5498,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A204" s="49" t="s">
         <v>272</v>
       </c>
@@ -5373,7 +5506,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A205" s="51" t="s">
         <v>272</v>
       </c>
@@ -5381,7 +5514,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A206" s="49" t="s">
         <v>272</v>
       </c>
@@ -5389,7 +5522,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A207" s="51" t="s">
         <v>272</v>
       </c>
@@ -5397,7 +5530,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A208" s="49" t="s">
         <v>272</v>
       </c>
@@ -5405,7 +5538,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A209" s="51" t="s">
         <v>272</v>
       </c>
@@ -5413,7 +5546,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A210" s="49" t="s">
         <v>272</v>
       </c>
@@ -5421,7 +5554,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A211" s="51" t="s">
         <v>272</v>
       </c>
@@ -5429,7 +5562,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A212" s="49" t="s">
         <v>272</v>
       </c>
@@ -5437,7 +5570,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A213" s="51" t="s">
         <v>272</v>
       </c>
@@ -5445,7 +5578,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A214" s="49" t="s">
         <v>272</v>
       </c>
@@ -5453,7 +5586,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A215" s="51" t="s">
         <v>272</v>
       </c>
@@ -5461,7 +5594,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A216" s="49" t="s">
         <v>272</v>
       </c>
@@ -5469,7 +5602,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A217" s="51" t="s">
         <v>272</v>
       </c>
@@ -5477,7 +5610,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A218" s="49" t="s">
         <v>272</v>
       </c>
@@ -5485,7 +5618,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A219" s="51" t="s">
         <v>272</v>
       </c>
@@ -5493,7 +5626,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A220" s="49" t="s">
         <v>272</v>
       </c>
@@ -5501,7 +5634,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A221" s="51" t="s">
         <v>272</v>
       </c>
@@ -5509,7 +5642,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A222" s="49" t="s">
         <v>293</v>
       </c>
@@ -5517,7 +5650,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A223" s="51" t="s">
         <v>293</v>
       </c>
@@ -5525,7 +5658,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A224" s="49" t="s">
         <v>293</v>
       </c>
@@ -5533,7 +5666,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A225" s="51" t="s">
         <v>293</v>
       </c>
@@ -5541,7 +5674,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A226" s="49" t="s">
         <v>293</v>
       </c>
@@ -5549,7 +5682,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A227" s="51" t="s">
         <v>293</v>
       </c>
@@ -5557,7 +5690,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A228" s="49" t="s">
         <v>293</v>
       </c>
@@ -5565,7 +5698,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A229" s="51" t="s">
         <v>293</v>
       </c>
@@ -5573,7 +5706,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A230" s="49" t="s">
         <v>293</v>
       </c>
@@ -5581,7 +5714,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A231" s="49" t="s">
         <v>303</v>
       </c>
@@ -5589,7 +5722,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A232" s="51" t="s">
         <v>303</v>
       </c>
@@ -5597,7 +5730,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A233" s="49" t="s">
         <v>303</v>
       </c>
@@ -5605,7 +5738,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A234" s="51" t="s">
         <v>303</v>
       </c>
@@ -5613,7 +5746,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A235" s="49" t="s">
         <v>303</v>
       </c>
@@ -5621,7 +5754,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A236" s="51" t="s">
         <v>303</v>
       </c>
@@ -5629,7 +5762,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A237" s="49" t="s">
         <v>303</v>
       </c>
@@ -5637,7 +5770,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A238" s="51" t="s">
         <v>303</v>
       </c>
@@ -5645,7 +5778,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A239" s="49" t="s">
         <v>303</v>
       </c>
@@ -5653,7 +5786,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A240" s="51" t="s">
         <v>303</v>
       </c>
@@ -5661,7 +5794,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A241" s="49" t="s">
         <v>303</v>
       </c>
@@ -5669,7 +5802,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A242" s="51" t="s">
         <v>303</v>
       </c>
@@ -5677,7 +5810,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A243" s="49" t="s">
         <v>303</v>
       </c>
@@ -5685,7 +5818,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A244" s="51" t="s">
         <v>303</v>
       </c>
@@ -5693,7 +5826,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A245" s="49" t="s">
         <v>303</v>
       </c>
@@ -5701,7 +5834,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A246" s="51" t="s">
         <v>303</v>
       </c>
@@ -5709,7 +5842,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A247" s="49" t="s">
         <v>303</v>
       </c>
@@ -5717,7 +5850,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A248" s="51" t="s">
         <v>303</v>
       </c>
@@ -5725,7 +5858,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A249" s="49" t="s">
         <v>303</v>
       </c>
@@ -5733,7 +5866,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A250" s="51" t="s">
         <v>303</v>
       </c>
@@ -5741,7 +5874,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A251" s="49" t="s">
         <v>303</v>
       </c>
@@ -5749,7 +5882,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A252" s="51" t="s">
         <v>303</v>
       </c>
@@ -5757,7 +5890,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A253" s="49" t="s">
         <v>325</v>
       </c>
@@ -5765,7 +5898,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A254" s="51" t="s">
         <v>325</v>
       </c>
@@ -5773,7 +5906,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A255" s="49" t="s">
         <v>325</v>
       </c>
@@ -5781,7 +5914,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A256" s="51" t="s">
         <v>325</v>
       </c>
@@ -5789,7 +5922,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A257" s="49" t="s">
         <v>325</v>
       </c>
@@ -5797,7 +5930,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A258" s="51" t="s">
         <v>325</v>
       </c>
@@ -5805,7 +5938,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A259" s="49" t="s">
         <v>325</v>
       </c>
@@ -5813,7 +5946,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A260" s="51" t="s">
         <v>325</v>
       </c>
@@ -5821,7 +5954,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A261" s="49" t="s">
         <v>325</v>
       </c>
@@ -5829,7 +5962,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A262" s="51" t="s">
         <v>325</v>
       </c>
@@ -5837,7 +5970,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A263" s="49" t="s">
         <v>325</v>
       </c>
@@ -5845,7 +5978,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A264" s="51" t="s">
         <v>325</v>
       </c>
@@ -5853,7 +5986,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A265" s="49" t="s">
         <v>325</v>
       </c>
@@ -5861,7 +5994,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A266" s="51" t="s">
         <v>325</v>
       </c>
@@ -5869,7 +6002,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A267" s="49" t="s">
         <v>325</v>
       </c>
@@ -5877,7 +6010,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A268" s="51" t="s">
         <v>325</v>
       </c>
@@ -5885,7 +6018,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A269" s="49" t="s">
         <v>325</v>
       </c>
@@ -5893,7 +6026,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A270" s="51" t="s">
         <v>325</v>
       </c>
@@ -5901,7 +6034,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A271" s="49" t="s">
         <v>325</v>
       </c>
@@ -5909,7 +6042,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A272" s="49" t="s">
         <v>344</v>
       </c>
@@ -5917,7 +6050,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="273" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A273" s="51" t="s">
         <v>344</v>
       </c>
@@ -5925,7 +6058,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="274" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A274" s="49" t="s">
         <v>344</v>
       </c>
@@ -5933,7 +6066,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="275" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A275" s="51" t="s">
         <v>344</v>
       </c>
@@ -5941,7 +6074,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="276" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A276" s="49" t="s">
         <v>344</v>
       </c>
@@ -5949,7 +6082,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="277" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A277" s="51" t="s">
         <v>344</v>
       </c>
@@ -5957,7 +6090,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="278" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A278" s="49" t="s">
         <v>344</v>
       </c>
@@ -5965,7 +6098,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="279" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A279" s="51" t="s">
         <v>344</v>
       </c>
@@ -5973,7 +6106,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="280" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A280" s="49" t="s">
         <v>344</v>
       </c>
@@ -5981,7 +6114,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="281" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A281" s="51" t="s">
         <v>344</v>
       </c>
@@ -5989,7 +6122,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="282" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A282" s="49" t="s">
         <v>344</v>
       </c>
@@ -5997,7 +6130,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="283" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A283" s="51" t="s">
         <v>344</v>
       </c>
@@ -6005,7 +6138,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="284" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A284" s="49" t="s">
         <v>344</v>
       </c>
@@ -6013,7 +6146,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="285" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A285" s="51" t="s">
         <v>344</v>
       </c>
@@ -6021,7 +6154,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="286" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A286" s="49" t="s">
         <v>344</v>
       </c>
@@ -6029,7 +6162,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="287" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A287" s="51" t="s">
         <v>344</v>
       </c>
@@ -6037,7 +6170,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A288" s="49" t="s">
         <v>361</v>
       </c>
@@ -6045,7 +6178,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="289" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A289" s="51" t="s">
         <v>361</v>
       </c>
@@ -6053,7 +6186,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="290" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A290" s="49" t="s">
         <v>361</v>
       </c>
@@ -6061,7 +6194,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A291" s="51" t="s">
         <v>361</v>
       </c>
@@ -6069,7 +6202,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="292" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A292" s="49" t="s">
         <v>361</v>
       </c>
@@ -6077,7 +6210,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="293" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A293" s="51" t="s">
         <v>361</v>
       </c>
@@ -6085,7 +6218,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="294" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A294" s="49" t="s">
         <v>361</v>
       </c>
@@ -6093,7 +6226,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="295" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A295" s="51" t="s">
         <v>361</v>
       </c>
@@ -6101,7 +6234,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="296" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A296" s="49" t="s">
         <v>361</v>
       </c>
@@ -6109,7 +6242,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="297" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A297" s="51" t="s">
         <v>361</v>
       </c>
@@ -6117,7 +6250,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="298" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A298" s="49" t="s">
         <v>361</v>
       </c>
@@ -6125,7 +6258,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="299" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A299" s="51" t="s">
         <v>361</v>
       </c>
@@ -6133,7 +6266,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="300" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A300" s="49" t="s">
         <v>361</v>
       </c>
@@ -6141,7 +6274,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="301" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A301" s="51" t="s">
         <v>361</v>
       </c>
@@ -6149,7 +6282,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="302" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A302" s="49" t="s">
         <v>361</v>
       </c>
@@ -6157,7 +6290,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A303" s="51" t="s">
         <v>361</v>
       </c>
@@ -6165,7 +6298,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A304" s="49" t="s">
         <v>361</v>
       </c>
@@ -6173,7 +6306,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="305" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A305" s="51" t="s">
         <v>361</v>
       </c>
@@ -6181,7 +6314,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="306" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A306" s="49" t="s">
         <v>361</v>
       </c>
@@ -6189,7 +6322,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="307" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A307" s="51" t="s">
         <v>361</v>
       </c>
@@ -6197,7 +6330,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="308" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A308" s="49" t="s">
         <v>361</v>
       </c>
@@ -6205,7 +6338,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="309" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A309" s="51" t="s">
         <v>361</v>
       </c>
@@ -6213,7 +6346,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="310" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A310" s="49" t="s">
         <v>361</v>
       </c>
@@ -6221,7 +6354,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="311" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A311" s="51" t="s">
         <v>361</v>
       </c>
@@ -6229,7 +6362,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="312" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A312" s="49" t="s">
         <v>361</v>
       </c>
@@ -6237,7 +6370,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="313" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A313" s="51" t="s">
         <v>361</v>
       </c>
@@ -6245,7 +6378,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="314" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A314" s="49" t="s">
         <v>361</v>
       </c>
@@ -6253,7 +6386,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="315" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A315" s="51" t="s">
         <v>361</v>
       </c>
@@ -6261,7 +6394,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="316" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A316" s="49" t="s">
         <v>361</v>
       </c>
@@ -6269,7 +6402,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="317" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A317" s="51" t="s">
         <v>361</v>
       </c>
@@ -6277,7 +6410,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="318" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A318" s="49" t="s">
         <v>361</v>
       </c>
@@ -6285,7 +6418,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="319" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A319" s="49" t="s">
         <v>393</v>
       </c>
@@ -6293,7 +6426,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="320" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A320" s="51" t="s">
         <v>393</v>
       </c>
@@ -6301,7 +6434,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A321" s="49" t="s">
         <v>393</v>
       </c>
@@ -6309,7 +6442,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A322" s="51" t="s">
         <v>393</v>
       </c>
@@ -6317,7 +6450,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A323" s="49" t="s">
         <v>393</v>
       </c>
@@ -6325,7 +6458,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A324" s="51" t="s">
         <v>393</v>
       </c>
@@ -6333,7 +6466,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A325" s="49" t="s">
         <v>393</v>
       </c>
@@ -6341,7 +6474,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A326" s="51" t="s">
         <v>393</v>
       </c>
@@ -6349,7 +6482,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A327" s="49" t="s">
         <v>393</v>
       </c>
@@ -6357,7 +6490,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A328" s="51" t="s">
         <v>393</v>
       </c>
@@ -6365,7 +6498,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A329" s="49" t="s">
         <v>393</v>
       </c>
@@ -6373,7 +6506,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A330" s="51" t="s">
         <v>393</v>
       </c>
@@ -6381,7 +6514,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A331" s="49" t="s">
         <v>393</v>
       </c>
@@ -6389,7 +6522,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A332" s="51" t="s">
         <v>393</v>
       </c>
@@ -6397,7 +6530,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A333" s="49" t="s">
         <v>393</v>
       </c>
@@ -6405,7 +6538,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A334" s="51" t="s">
         <v>393</v>
       </c>
@@ -6413,7 +6546,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A335" s="49" t="s">
         <v>393</v>
       </c>
@@ -6421,7 +6554,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A336" s="51" t="s">
         <v>393</v>
       </c>
@@ -6429,7 +6562,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A337" s="49" t="s">
         <v>393</v>
       </c>
@@ -6437,7 +6570,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A338" s="51" t="s">
         <v>393</v>
       </c>
@@ -6445,7 +6578,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A339" s="49" t="s">
         <v>393</v>
       </c>
@@ -6453,7 +6586,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A340" s="51" t="s">
         <v>393</v>
       </c>
@@ -6461,7 +6594,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A341" s="49" t="s">
         <v>393</v>
       </c>
@@ -6469,7 +6602,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A342" s="51" t="s">
         <v>393</v>
       </c>
@@ -6477,7 +6610,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A343" s="49" t="s">
         <v>393</v>
       </c>
@@ -6485,7 +6618,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A344" s="51" t="s">
         <v>393</v>
       </c>
@@ -6493,7 +6626,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A345" s="49" t="s">
         <v>393</v>
       </c>
@@ -6501,7 +6634,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A346" s="51" t="s">
         <v>393</v>
       </c>
@@ -6509,7 +6642,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A347" s="49" t="s">
         <v>393</v>
       </c>
@@ -6517,7 +6650,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A348" s="51" t="s">
         <v>393</v>
       </c>
@@ -6525,7 +6658,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A349" s="49" t="s">
         <v>393</v>
       </c>
@@ -6533,7 +6666,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A350" s="51" t="s">
         <v>393</v>
       </c>
@@ -6541,7 +6674,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A351" s="49" t="s">
         <v>393</v>
       </c>
@@ -6549,7 +6682,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="A352" s="51" t="s">
         <v>393</v>
       </c>
@@ -6569,18 +6702,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.88671875" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="25"/>
+    <col min="6" max="6" width="28.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="25.9">
       <c r="A1" s="30" t="s">
         <v>428</v>
       </c>
@@ -6600,7 +6733,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="18">
       <c r="A2" s="32" t="s">
         <v>434</v>
       </c>
@@ -6620,7 +6753,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="32" t="s">
         <v>434</v>
       </c>
@@ -6641,7 +6774,7 @@
         <v>14542.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="18">
       <c r="A4" s="32" t="s">
         <v>434</v>
       </c>
@@ -6662,7 +6795,7 @@
         <v>14311.5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="18">
       <c r="A5" s="32" t="s">
         <v>434</v>
       </c>
@@ -6683,7 +6816,7 @@
         <v>14689.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="32" t="s">
         <v>434</v>
       </c>
@@ -6704,7 +6837,7 @@
         <v>13251</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="32" t="s">
         <v>434</v>
       </c>
@@ -6725,7 +6858,7 @@
         <v>10762.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="32" t="s">
         <v>434</v>
       </c>
@@ -6746,7 +6879,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="32" t="s">
         <v>434</v>
       </c>
@@ -6767,7 +6900,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="32" t="s">
         <v>434</v>
       </c>
@@ -6788,7 +6921,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="32" t="s">
         <v>434</v>
       </c>
@@ -6809,7 +6942,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="35" t="s">
         <v>436</v>
       </c>
@@ -6830,7 +6963,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="35" t="s">
         <v>436</v>
       </c>
@@ -6851,7 +6984,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="35" t="s">
         <v>436</v>
       </c>
@@ -6872,7 +7005,7 @@
         <v>4231.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="38" t="s">
         <v>440</v>
       </c>
@@ -6893,7 +7026,7 @@
         <v>8494.5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="41" t="s">
         <v>442</v>
       </c>
@@ -6914,7 +7047,7 @@
         <v>13314</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="41" t="s">
         <v>442</v>
       </c>
@@ -6935,7 +7068,7 @@
         <v>8662.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="41" t="s">
         <v>442</v>
       </c>
@@ -6956,7 +7089,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="44" t="s">
         <v>445</v>
       </c>
@@ -6977,7 +7110,7 @@
         <v>14164.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="44" t="s">
         <v>445</v>
       </c>
@@ -6998,7 +7131,7 @@
         <v>13723.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="44" t="s">
         <v>445</v>
       </c>
@@ -7019,7 +7152,7 @@
         <v>13377</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="44" t="s">
         <v>445</v>
       </c>
@@ -7040,7 +7173,7 @@
         <v>10027.5</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="44" t="s">
         <v>445</v>
       </c>
@@ -7061,7 +7194,7 @@
         <v>10384.5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="44" t="s">
         <v>445</v>
       </c>
@@ -7082,7 +7215,7 @@
         <v>4620</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="44" t="s">
         <v>445</v>
       </c>
@@ -7103,7 +7236,7 @@
         <v>4368</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="44" t="s">
         <v>445</v>
       </c>
@@ -7124,7 +7257,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="44" t="s">
         <v>445</v>
       </c>
@@ -7145,98 +7278,98 @@
         <v>1144.5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="29"/>
     </row>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="29"/>
     </row>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
       <c r="E30" s="29"/>
     </row>
-    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
       <c r="E31" s="29"/>
     </row>
-    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
       <c r="E32" s="29"/>
     </row>
-    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
       <c r="E33" s="29"/>
     </row>
-    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
       <c r="E34" s="29"/>
     </row>
-    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="27"/>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
       <c r="E35" s="29"/>
     </row>
-    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="27"/>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
       <c r="E36" s="29"/>
     </row>
-    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="27"/>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
       <c r="E37" s="29"/>
     </row>
-    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="27"/>
       <c r="B38" s="28"/>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
       <c r="E38" s="29"/>
     </row>
-    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A39" s="27"/>
       <c r="B39" s="28"/>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
       <c r="E39" s="29"/>
     </row>
-    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A40" s="27"/>
       <c r="B40" s="28"/>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
       <c r="E40" s="29"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="E41" s="26"/>
     </row>
   </sheetData>
@@ -7248,768 +7381,768 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1DC0BE-3C08-4CFF-8806-21F8A4247F7D}">
   <dimension ref="A1:B95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="75.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="53" t="s">
         <v>446</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="53" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:2">
+      <c r="A2" s="53">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:2">
+      <c r="A3" s="53">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="53" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:2">
+      <c r="A4" s="53">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="53" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:2">
+      <c r="A5" s="53">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="53" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:2">
+      <c r="A6" s="53">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="53" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:2">
+      <c r="A7" s="53">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="53" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:2">
+      <c r="A8" s="53">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:2">
+      <c r="A9" s="53">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:2">
+      <c r="A10" s="53">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:2">
+      <c r="A11" s="53">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:2">
+      <c r="A12" s="53">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:2">
+      <c r="A13" s="53">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:2">
+      <c r="A14" s="53">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:2">
+      <c r="A15" s="53">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="16" spans="1:2">
+      <c r="A16" s="53">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:2">
+      <c r="A17" s="53">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:2">
+      <c r="A18" s="53">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:2">
+      <c r="A19" s="53">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:2">
+      <c r="A20" s="53">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="21" spans="1:2">
+      <c r="A21" s="53">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:2">
+      <c r="A22" s="53">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:2">
+      <c r="A23" s="53">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:2">
+      <c r="A24" s="53">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="53" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:2">
+      <c r="A25" s="53">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="53" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="26" spans="1:2">
+      <c r="A26" s="53">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="53" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:2">
+      <c r="A27" s="53">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="53" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="28" spans="1:2">
+      <c r="A28" s="53">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="53" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="29" spans="1:2">
+      <c r="A29" s="53">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="53" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="30" spans="1:2">
+      <c r="A30" s="53">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="53" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="31" spans="1:2">
+      <c r="A31" s="53">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="53" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="32" spans="1:2">
+      <c r="A32" s="53">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="53" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="33" spans="1:2">
+      <c r="A33" s="53">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="53" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="34" spans="1:2">
+      <c r="A34" s="53">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="53" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="35" spans="1:2">
+      <c r="A35" s="53">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="53" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="36" spans="1:2">
+      <c r="A36" s="53">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="53" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="37" spans="1:2">
+      <c r="A37" s="53">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="53" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="38" spans="1:2">
+      <c r="A38" s="53">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="53" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
+    <row r="39" spans="1:2">
+      <c r="A39" s="53">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="53" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="40" spans="1:2">
+      <c r="A40" s="53">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="53" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
+    <row r="41" spans="1:2">
+      <c r="A41" s="53">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="53" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="42" spans="1:2">
+      <c r="A42" s="53">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="53" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
+    <row r="43" spans="1:2">
+      <c r="A43" s="53">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="44" spans="1:2">
+      <c r="A44" s="53">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
+    <row r="45" spans="1:2">
+      <c r="A45" s="53">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
+    <row r="46" spans="1:2">
+      <c r="A46" s="53">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="53" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="47" spans="1:2">
+      <c r="A47" s="53">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48">
+    <row r="48" spans="1:2">
+      <c r="A48" s="53">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49">
+    <row r="49" spans="1:2">
+      <c r="A49" s="53">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50">
+    <row r="50" spans="1:2">
+      <c r="A50" s="53">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51">
+    <row r="51" spans="1:2">
+      <c r="A51" s="53">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52">
+    <row r="52" spans="1:2">
+      <c r="A52" s="53">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53">
+    <row r="53" spans="1:2">
+      <c r="A53" s="53">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54">
+    <row r="54" spans="1:2">
+      <c r="A54" s="53">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55">
+    <row r="55" spans="1:2">
+      <c r="A55" s="53">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="53" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56">
+    <row r="56" spans="1:2">
+      <c r="A56" s="53">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="53" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57">
+    <row r="57" spans="1:2">
+      <c r="A57" s="53">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="53" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58">
+    <row r="58" spans="1:2">
+      <c r="A58" s="53">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="53" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59">
+    <row r="59" spans="1:2">
+      <c r="A59" s="53">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="53" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60">
+    <row r="60" spans="1:2">
+      <c r="A60" s="53">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="53" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61">
+    <row r="61" spans="1:2">
+      <c r="A61" s="53">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="53" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62">
+    <row r="62" spans="1:2">
+      <c r="A62" s="53">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="53" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63">
+    <row r="63" spans="1:2">
+      <c r="A63" s="53">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="53" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64">
+    <row r="64" spans="1:2">
+      <c r="A64" s="53">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="53" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65">
+    <row r="65" spans="1:2">
+      <c r="A65" s="53">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="53" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66">
+    <row r="66" spans="1:2">
+      <c r="A66" s="53">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="53" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67">
+    <row r="67" spans="1:2">
+      <c r="A67" s="53">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="53" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68">
+    <row r="68" spans="1:2">
+      <c r="A68" s="53">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="53" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69">
+    <row r="69" spans="1:2">
+      <c r="A69" s="53">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="53" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70">
+    <row r="70" spans="1:2">
+      <c r="A70" s="53">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="53" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71">
+    <row r="71" spans="1:2">
+      <c r="A71" s="53">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="53" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72">
+    <row r="72" spans="1:2">
+      <c r="A72" s="53">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="53" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73">
+    <row r="73" spans="1:2">
+      <c r="A73" s="53">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="53" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74">
+    <row r="74" spans="1:2">
+      <c r="A74" s="53">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="53" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75">
+    <row r="75" spans="1:2">
+      <c r="A75" s="53">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="53" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76">
+    <row r="76" spans="1:2">
+      <c r="A76" s="53">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="53" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77">
+    <row r="77" spans="1:2">
+      <c r="A77" s="53">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="53" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78">
+    <row r="78" spans="1:2">
+      <c r="A78" s="53">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="53" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79">
+    <row r="79" spans="1:2">
+      <c r="A79" s="53">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="53" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80">
+    <row r="80" spans="1:2">
+      <c r="A80" s="53">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="53" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81">
+    <row r="81" spans="1:2">
+      <c r="A81" s="53">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="53" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82">
+    <row r="82" spans="1:2">
+      <c r="A82" s="53">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="53" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83">
+    <row r="83" spans="1:2">
+      <c r="A83" s="53">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="53" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84">
+    <row r="84" spans="1:2">
+      <c r="A84" s="53">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="53" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85">
+    <row r="85" spans="1:2">
+      <c r="A85" s="53">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="53" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86">
+    <row r="86" spans="1:2">
+      <c r="A86" s="53">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="53" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87">
+    <row r="87" spans="1:2">
+      <c r="A87" s="53">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="53" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88">
+    <row r="88" spans="1:2">
+      <c r="A88" s="53">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="53" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89">
+    <row r="89" spans="1:2">
+      <c r="A89" s="53">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="53" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90">
+    <row r="90" spans="1:2">
+      <c r="A90" s="53">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="53" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91">
+    <row r="91" spans="1:2">
+      <c r="A91" s="53">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="53" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92">
+    <row r="92" spans="1:2">
+      <c r="A92" s="53">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="53" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93">
+    <row r="93" spans="1:2">
+      <c r="A93" s="53">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="53" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94">
+    <row r="94" spans="1:2">
+      <c r="A94" s="53">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="53" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95">
+    <row r="95" spans="1:2">
+      <c r="A95" s="53">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="53" t="s">
         <v>514</v>
       </c>
     </row>
@@ -8025,238 +8158,239 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376B93B6-7CD8-4B1C-BCCE-53C84FB0C94C}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="75.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="53" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B1" s="53"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="53">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="53" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:2">
+      <c r="A4" s="53">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="53" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:2">
+      <c r="A5" s="53">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="53" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:2">
+      <c r="A6" s="53">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="53" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:2">
+      <c r="A7" s="53">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="53" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:2">
+      <c r="A8" s="53">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="53" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:2">
+      <c r="A9" s="53">
         <v>31</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="53" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:2">
+      <c r="A10" s="53">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="53" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:2">
+      <c r="A11" s="53">
         <v>37</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="53" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:2">
+      <c r="A12" s="53">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="53" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:2">
+      <c r="A13" s="53">
         <v>40</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="53" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:2">
+      <c r="A14" s="53">
         <v>41</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="53" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:2">
+      <c r="A15" s="53">
         <v>45</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="53" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="16" spans="1:2">
+      <c r="A16" s="53">
         <v>60</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="53" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:2">
+      <c r="A17" s="53">
         <v>61</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="53" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:2">
+      <c r="A18" s="53">
         <v>66</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="53" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:2">
+      <c r="A19" s="53">
         <v>67</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="53" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:2">
+      <c r="A20" s="53">
         <v>69</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="53" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="21" spans="1:2">
+      <c r="A21" s="53">
         <v>70</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="53" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:2">
+      <c r="A22" s="53">
         <v>71</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="53" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:2">
+      <c r="A23" s="53">
         <v>72</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="53" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:2">
+      <c r="A24" s="53">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="53" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:2">
+      <c r="A25" s="53">
         <v>74</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="53" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="26" spans="1:2">
+      <c r="A26" s="53">
         <v>75</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="53" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:2">
+      <c r="A27" s="53">
         <v>76</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="53" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="28" spans="1:2">
+      <c r="A28" s="53">
         <v>77</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="53" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="29" spans="1:2">
+      <c r="A29" s="53">
         <v>84</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="53" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="30" spans="1:2">
+      <c r="A30" s="53">
         <v>85</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="53" t="s">
         <v>505</v>
       </c>
     </row>
@@ -8268,221 +8402,222 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29A849C-0396-4A45-9316-83F0776D4FED}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="3" width="68" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="53" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B1" s="53"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="53">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="53" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:2">
+      <c r="A4" s="53">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="53" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:2">
+      <c r="A5" s="53">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="53" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:2">
+      <c r="A6" s="53">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="53" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:2">
+      <c r="A7" s="53">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="53" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:2">
+      <c r="A8" s="53">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="53" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:2">
+      <c r="A9" s="53">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="53" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:2">
+      <c r="A10" s="53">
         <v>33</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="53" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:2">
+      <c r="A11" s="53">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="53" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:2">
+      <c r="A12" s="53">
         <v>35</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="53" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:2">
+      <c r="A13" s="53">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="53" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:2">
+      <c r="A14" s="53">
         <v>68</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="53" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="15" spans="1:2">
+      <c r="A15" s="53">
         <v>78</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="53" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="16" spans="1:2">
+      <c r="A16" s="53">
         <v>79</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="53" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="17" spans="1:2">
+      <c r="A17" s="53">
         <v>80</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="53" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="18" spans="1:2">
+      <c r="A18" s="53">
         <v>81</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="53" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="19" spans="1:2">
+      <c r="A19" s="53">
         <v>82</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="53" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="20" spans="1:2">
+      <c r="A20" s="53">
         <v>83</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="53" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="21" spans="1:2">
+      <c r="A21" s="53">
         <v>86</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="53" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="22" spans="1:2">
+      <c r="A22" s="53">
         <v>87</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="53" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="23" spans="1:2">
+      <c r="A23" s="53">
         <v>88</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="53" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:2">
+      <c r="A24" s="53">
         <v>89</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="53" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="25" spans="1:2">
+      <c r="A25" s="53">
         <v>90</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="53" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="26" spans="1:2">
+      <c r="A26" s="53">
         <v>92</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="53" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="27" spans="1:2">
+      <c r="A27" s="53">
         <v>93</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="53" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="28" spans="1:2">
+      <c r="A28" s="53">
         <v>94</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="53" t="s">
         <v>514</v>
       </c>
     </row>
@@ -8494,134 +8629,136 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7476908D-3A9A-4301-9740-379B31A7722E}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="53" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="53">
         <v>64</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="53" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4" spans="1:3">
+      <c r="A4" s="53">
         <v>58</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="53" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:3">
+      <c r="A5" s="53">
         <v>62</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="53" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="6" spans="1:3">
+      <c r="A6" s="53">
         <v>63</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="53" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:3">
+      <c r="A7" s="53">
         <v>91</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="53" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
+    <row r="8" spans="1:3">
+      <c r="A8" s="53">
         <v>54</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="53" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:3">
+      <c r="A9" s="53">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="53" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="10" spans="1:3">
+      <c r="A10" s="53">
         <v>59</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="53" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:3">
+      <c r="A11" s="53">
         <v>56</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="53" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
+    <row r="12" spans="1:3">
+      <c r="A12" s="53">
         <v>55</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="53" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="13" spans="1:3">
+      <c r="A13" s="53">
         <v>65</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="53" t="s">
         <v>518</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="53" t="s">
         <v>485</v>
       </c>
     </row>
@@ -8633,402 +8770,442 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC53B66-DA17-482E-B0A4-0607724DBC4A}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="75.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="75.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="54" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="53" t="s">
         <v>519</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="53" t="s">
         <v>520</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="53" t="s">
         <v>521</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="53" t="s">
         <v>522</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="53" t="s">
         <v>523</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="53" t="s">
         <v>524</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="53" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="53" t="s">
         <v>456</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="53" t="s">
         <v>459</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="53" t="s">
         <v>456</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="53" t="s">
         <v>456</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="53" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G3" s="53"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="53" t="s">
         <v>457</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="53" t="s">
         <v>461</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="53" t="s">
         <v>457</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="53" t="s">
         <v>468</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="53" t="s">
         <v>457</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="53" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="G4" s="53"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="53" t="s">
         <v>458</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="53" t="s">
         <v>462</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="53" t="s">
         <v>458</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="53" t="s">
         <v>473</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="53" t="s">
         <v>458</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="53" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="G5" s="53"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="53" t="s">
         <v>459</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="53" t="s">
         <v>460</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="53" t="s">
         <v>489</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="53" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="G6" s="53"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="53" t="s">
         <v>461</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="53" t="s">
         <v>470</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="53" t="s">
         <v>473</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="53" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="G7" s="53"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="53" t="s">
         <v>462</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="53" t="s">
         <v>472</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="53" t="s">
         <v>471</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="53" t="s">
         <v>491</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="53" t="s">
         <v>489</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="53" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="G8" s="53"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="53" t="s">
         <v>473</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="53" t="s">
         <v>473</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="53" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="G9" s="53"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="53" t="s">
         <v>470</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="53" t="s">
         <v>480</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="53" t="s">
         <v>489</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="53" t="s">
         <v>491</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="53" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="G10" s="53"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="53" t="s">
         <v>472</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="53" t="s">
         <v>481</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="53" t="s">
         <v>494</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="53" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="G11" s="53"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="53" t="s">
         <v>473</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="53" t="s">
         <v>487</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="53" t="s">
         <v>491</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="53" t="s">
         <v>495</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="53" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="G12" s="53"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="53" t="s">
         <v>480</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="53" t="s">
         <v>489</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="53" t="s">
         <v>496</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="53" t="s">
         <v>494</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="53" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="G13" s="53"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="53" t="s">
         <v>481</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="53" t="s">
         <v>497</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="53" t="s">
         <v>496</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="53" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="G14" s="53"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="53" t="s">
         <v>486</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="53" t="s">
         <v>491</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="53" t="s">
         <v>494</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="53" t="s">
         <v>504</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="53" t="s">
         <v>497</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="53" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="G15" s="53"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="53" t="s">
         <v>489</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="53" t="s">
         <v>496</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="53" t="s">
         <v>505</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="53" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="53" t="s">
         <v>490</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="53" t="s">
         <v>497</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D17" s="53"/>
+      <c r="E17" s="53" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="53" t="s">
         <v>491</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="53" t="s">
         <v>494</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="53" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="53" t="s">
         <v>492</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="53" t="s">
         <v>495</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="53" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="53" t="s">
         <v>493</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="53" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="53" t="s">
         <v>494</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="53" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="53" t="s">
         <v>496</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="53" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="53" t="s">
         <v>497</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="53" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="53" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="53" t="s">
         <v>505</v>
       </c>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/LORRY DAILY PLANNING.xlsx
+++ b/data/LORRY DAILY PLANNING.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{48CB7717-6537-4BC5-9C99-A54C2B20752F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACFA8ED7-0D89-4BBB-B357-B3CE536EF5BD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79570862-D42D-4D37-8A8D-E6509371ECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6" xr2:uid="{E2E94725-398A-4689-AFDE-8CD3FEFE47E9}"/>
   </bookViews>
   <sheets>
     <sheet name="VIVIAN" sheetId="3" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="866">
   <si>
     <t>NO</t>
   </si>
@@ -1717,13 +1717,946 @@
   </si>
   <si>
     <t>EVERY DAY</t>
+  </si>
+  <si>
+    <t>POSTCODE</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>46000</t>
+  </si>
+  <si>
+    <t>47500</t>
+  </si>
+  <si>
+    <t>41000</t>
+  </si>
+  <si>
+    <t>68000</t>
+  </si>
+  <si>
+    <t>43200</t>
+  </si>
+  <si>
+    <t>47100</t>
+  </si>
+  <si>
+    <t>48000</t>
+  </si>
+  <si>
+    <t>43900</t>
+  </si>
+  <si>
+    <t>42700</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>45200</t>
+  </si>
+  <si>
+    <t>44000</t>
+  </si>
+  <si>
+    <t>43500</t>
+  </si>
+  <si>
+    <t>43000</t>
+  </si>
+  <si>
+    <t>43650</t>
+  </si>
+  <si>
+    <t>42600</t>
+  </si>
+  <si>
+    <t>42500</t>
+  </si>
+  <si>
+    <t>42800</t>
+  </si>
+  <si>
+    <t>41050</t>
+  </si>
+  <si>
+    <t>42200</t>
+  </si>
+  <si>
+    <t>42920</t>
+  </si>
+  <si>
+    <t>43300</t>
+  </si>
+  <si>
+    <t>43400</t>
+  </si>
+  <si>
+    <t>57000</t>
+  </si>
+  <si>
+    <t>47810</t>
+  </si>
+  <si>
+    <t>47000</t>
+  </si>
+  <si>
+    <t>50350</t>
+  </si>
+  <si>
+    <t>50470</t>
+  </si>
+  <si>
+    <t>59100</t>
+  </si>
+  <si>
+    <t>50480</t>
+  </si>
+  <si>
+    <t>52100</t>
+  </si>
+  <si>
+    <t>51100</t>
+  </si>
+  <si>
+    <t>53300</t>
+  </si>
+  <si>
+    <t>53200</t>
+  </si>
+  <si>
+    <t>58000</t>
+  </si>
+  <si>
+    <t>56000</t>
+  </si>
+  <si>
+    <t>57100</t>
+  </si>
+  <si>
+    <t>51200</t>
+  </si>
+  <si>
+    <t>50490</t>
+  </si>
+  <si>
+    <t>55100</t>
+  </si>
+  <si>
+    <t>54200</t>
+  </si>
+  <si>
+    <t>58100</t>
+  </si>
+  <si>
+    <t>58200</t>
+  </si>
+  <si>
+    <t>47180</t>
+  </si>
+  <si>
+    <t>62000</t>
+  </si>
+  <si>
+    <t>63000</t>
+  </si>
+  <si>
+    <t>43800</t>
+  </si>
+  <si>
+    <t>62050</t>
+  </si>
+  <si>
+    <t>62100</t>
+  </si>
+  <si>
+    <t>62250</t>
+  </si>
+  <si>
+    <t>62300</t>
+  </si>
+  <si>
+    <t>62550</t>
+  </si>
+  <si>
+    <t>62150</t>
+  </si>
+  <si>
+    <t>87000</t>
+  </si>
+  <si>
+    <t>87020</t>
+  </si>
+  <si>
+    <t>87030</t>
+  </si>
+  <si>
+    <t>87033</t>
+  </si>
+  <si>
+    <t>87025</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>81300</t>
+  </si>
+  <si>
+    <t>81400</t>
+  </si>
+  <si>
+    <t>81000</t>
+  </si>
+  <si>
+    <t>79100</t>
+  </si>
+  <si>
+    <t>86000</t>
+  </si>
+  <si>
+    <t>84000</t>
+  </si>
+  <si>
+    <t>83000</t>
+  </si>
+  <si>
+    <t>82000</t>
+  </si>
+  <si>
+    <t>85000</t>
+  </si>
+  <si>
+    <t>81900</t>
+  </si>
+  <si>
+    <t>86800</t>
+  </si>
+  <si>
+    <t>84900</t>
+  </si>
+  <si>
+    <t>84600</t>
+  </si>
+  <si>
+    <t>86100</t>
+  </si>
+  <si>
+    <t>83700</t>
+  </si>
+  <si>
+    <t>86400</t>
+  </si>
+  <si>
+    <t>81750</t>
+  </si>
+  <si>
+    <t>81700</t>
+  </si>
+  <si>
+    <t>79200</t>
+  </si>
+  <si>
+    <t>81550</t>
+  </si>
+  <si>
+    <t>82100</t>
+  </si>
+  <si>
+    <t>86200</t>
+  </si>
+  <si>
+    <t>85400</t>
+  </si>
+  <si>
+    <t>85300</t>
+  </si>
+  <si>
+    <t>85010</t>
+  </si>
+  <si>
+    <t>86900</t>
+  </si>
+  <si>
+    <t>86700</t>
+  </si>
+  <si>
+    <t>71010</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>28000</t>
+  </si>
+  <si>
+    <t>28400</t>
+  </si>
+  <si>
+    <t>28700</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>27000</t>
+  </si>
+  <si>
+    <t>28200</t>
+  </si>
+  <si>
+    <t>28300</t>
+  </si>
+  <si>
+    <t>26500</t>
+  </si>
+  <si>
+    <t>26600</t>
+  </si>
+  <si>
+    <t>26800</t>
+  </si>
+  <si>
+    <t>27200</t>
+  </si>
+  <si>
+    <t>27300</t>
+  </si>
+  <si>
+    <t>28500</t>
+  </si>
+  <si>
+    <t>28600</t>
+  </si>
+  <si>
+    <t>27030</t>
+  </si>
+  <si>
+    <t>28060</t>
+  </si>
+  <si>
+    <t>39000</t>
+  </si>
+  <si>
+    <t>39200</t>
+  </si>
+  <si>
+    <t>49000</t>
+  </si>
+  <si>
+    <t>26700</t>
+  </si>
+  <si>
+    <t>26400</t>
+  </si>
+  <si>
+    <t>26300</t>
+  </si>
+  <si>
+    <t>26100</t>
+  </si>
+  <si>
+    <t>26080</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>32040</t>
+  </si>
+  <si>
+    <t>31000</t>
+  </si>
+  <si>
+    <t>31900</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>35800</t>
+  </si>
+  <si>
+    <t>36700</t>
+  </si>
+  <si>
+    <t>35500</t>
+  </si>
+  <si>
+    <t>32200</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
+    <t>34950</t>
+  </si>
+  <si>
+    <t>31250</t>
+  </si>
+  <si>
+    <t>31100</t>
+  </si>
+  <si>
+    <t>33000</t>
+  </si>
+  <si>
+    <t>33300</t>
+  </si>
+  <si>
+    <t>34350</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>34300</t>
+  </si>
+  <si>
+    <t>32400</t>
+  </si>
+  <si>
+    <t>45300</t>
+  </si>
+  <si>
+    <t>32100</t>
+  </si>
+  <si>
+    <t>34100</t>
+  </si>
+  <si>
+    <t>31600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>31400</t>
+  </si>
+  <si>
+    <t>31500</t>
+  </si>
+  <si>
+    <t>31450</t>
+  </si>
+  <si>
+    <t>30200</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>24300</t>
+  </si>
+  <si>
+    <t>23000</t>
+  </si>
+  <si>
+    <t>24100</t>
+  </si>
+  <si>
+    <t>21600</t>
+  </si>
+  <si>
+    <t>21700</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>22200</t>
+  </si>
+  <si>
+    <t>22300</t>
+  </si>
+  <si>
+    <t>23050</t>
+  </si>
+  <si>
+    <t>20200</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
+    <t>17500</t>
+  </si>
+  <si>
+    <t>18500</t>
+  </si>
+  <si>
+    <t>16800</t>
+  </si>
+  <si>
+    <t>16300</t>
+  </si>
+  <si>
+    <t>16200</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>18300</t>
+  </si>
+  <si>
+    <t>17600</t>
+  </si>
+  <si>
+    <t>17200</t>
+  </si>
+  <si>
+    <t>16250</t>
+  </si>
+  <si>
+    <t>16100</t>
+  </si>
+  <si>
+    <t>16150</t>
+  </si>
+  <si>
+    <t>17510</t>
+  </si>
+  <si>
+    <t>16350</t>
+  </si>
+  <si>
+    <t>05000</t>
+  </si>
+  <si>
+    <t>08000</t>
+  </si>
+  <si>
+    <t>09000</t>
+  </si>
+  <si>
+    <t>06000</t>
+  </si>
+  <si>
+    <t>06010</t>
+  </si>
+  <si>
+    <t>07000</t>
+  </si>
+  <si>
+    <t>09100</t>
+  </si>
+  <si>
+    <t>06200</t>
+  </si>
+  <si>
+    <t>08300</t>
+  </si>
+  <si>
+    <t>06700</t>
+  </si>
+  <si>
+    <t>06400</t>
+  </si>
+  <si>
+    <t>09700</t>
+  </si>
+  <si>
+    <t>06050</t>
+  </si>
+  <si>
+    <t>08100</t>
+  </si>
+  <si>
+    <t>09800</t>
+  </si>
+  <si>
+    <t>09300</t>
+  </si>
+  <si>
+    <t>08500</t>
+  </si>
+  <si>
+    <t>01000</t>
+  </si>
+  <si>
+    <t>02600</t>
+  </si>
+  <si>
+    <t>02100</t>
+  </si>
+  <si>
+    <t>02200</t>
+  </si>
+  <si>
+    <t>02000</t>
+  </si>
+  <si>
+    <t>02500</t>
+  </si>
+  <si>
+    <t>02300</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>14300</t>
+  </si>
+  <si>
+    <t>11900</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>13200</t>
+  </si>
+  <si>
+    <t>14200</t>
+  </si>
+  <si>
+    <t>13300</t>
+  </si>
+  <si>
+    <t>13500</t>
+  </si>
+  <si>
+    <t>11050</t>
+  </si>
+  <si>
+    <t>11200</t>
+  </si>
+  <si>
+    <t>11500</t>
+  </si>
+  <si>
+    <t>11600</t>
+  </si>
+  <si>
+    <t>11700</t>
+  </si>
+  <si>
+    <t>11960</t>
+  </si>
+  <si>
+    <t>13020</t>
+  </si>
+  <si>
+    <t>13700</t>
+  </si>
+  <si>
+    <t>13600</t>
+  </si>
+  <si>
+    <t>14100</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>71000</t>
+  </si>
+  <si>
+    <t>71800</t>
+  </si>
+  <si>
+    <t>71700</t>
+  </si>
+  <si>
+    <t>72100</t>
+  </si>
+  <si>
+    <t>72000</t>
+  </si>
+  <si>
+    <t>73000</t>
+  </si>
+  <si>
+    <t>73400</t>
+  </si>
+  <si>
+    <t>71300</t>
+  </si>
+  <si>
+    <t>72600</t>
+  </si>
+  <si>
+    <t>70450</t>
+  </si>
+  <si>
+    <t>71050</t>
+  </si>
+  <si>
+    <t>71200</t>
+  </si>
+  <si>
+    <t>73900</t>
+  </si>
+  <si>
+    <t>71400</t>
+  </si>
+  <si>
+    <t>70400</t>
+  </si>
+  <si>
+    <t>71900</t>
+  </si>
+  <si>
+    <t>71350</t>
+  </si>
+  <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>78000</t>
+  </si>
+  <si>
+    <t>77000</t>
+  </si>
+  <si>
+    <t>77300</t>
+  </si>
+  <si>
+    <t>78300</t>
+  </si>
+  <si>
+    <t>75450</t>
+  </si>
+  <si>
+    <t>75200</t>
+  </si>
+  <si>
+    <t>76400</t>
+  </si>
+  <si>
+    <t>77500</t>
+  </si>
+  <si>
+    <t>77200</t>
+  </si>
+  <si>
+    <t>75460</t>
+  </si>
+  <si>
+    <t>75350</t>
+  </si>
+  <si>
+    <t>78200</t>
+  </si>
+  <si>
+    <t>76300</t>
+  </si>
+  <si>
+    <t>76100</t>
+  </si>
+  <si>
+    <t>88000</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>91000</t>
+  </si>
+  <si>
+    <t>91100</t>
+  </si>
+  <si>
+    <t>89000</t>
+  </si>
+  <si>
+    <t>89800</t>
+  </si>
+  <si>
+    <t>89150</t>
+  </si>
+  <si>
+    <t>89300</t>
+  </si>
+  <si>
+    <t>91200</t>
+  </si>
+  <si>
+    <t>91308</t>
+  </si>
+  <si>
+    <t>89050</t>
+  </si>
+  <si>
+    <t>89600</t>
+  </si>
+  <si>
+    <t>89500</t>
+  </si>
+  <si>
+    <t>88200</t>
+  </si>
+  <si>
+    <t>89200</t>
+  </si>
+  <si>
+    <t>89100</t>
+  </si>
+  <si>
+    <t>89108</t>
+  </si>
+  <si>
+    <t>89650</t>
+  </si>
+  <si>
+    <t>89950</t>
+  </si>
+  <si>
+    <t>90100</t>
+  </si>
+  <si>
+    <t>90200</t>
+  </si>
+  <si>
+    <t>89850</t>
+  </si>
+  <si>
+    <t>89900</t>
+  </si>
+  <si>
+    <t>89740</t>
+  </si>
+  <si>
+    <t>89730</t>
+  </si>
+  <si>
+    <t>88400</t>
+  </si>
+  <si>
+    <t>88450</t>
+  </si>
+  <si>
+    <t>93000</t>
+  </si>
+  <si>
+    <t>98000</t>
+  </si>
+  <si>
+    <t>96000</t>
+  </si>
+  <si>
+    <t>97000</t>
+  </si>
+  <si>
+    <t>95000</t>
+  </si>
+  <si>
+    <t>96100</t>
+  </si>
+  <si>
+    <t>96800</t>
+  </si>
+  <si>
+    <t>96400</t>
+  </si>
+  <si>
+    <t>98700</t>
+  </si>
+  <si>
+    <t>98850</t>
+  </si>
+  <si>
+    <t>98050</t>
+  </si>
+  <si>
+    <t>94700</t>
+  </si>
+  <si>
+    <t>95700</t>
+  </si>
+  <si>
+    <t>96700</t>
+  </si>
+  <si>
+    <t>96750</t>
+  </si>
+  <si>
+    <t>96600</t>
+  </si>
+  <si>
+    <t>96300</t>
+  </si>
+  <si>
+    <t>95400</t>
+  </si>
+  <si>
+    <t>95408</t>
+  </si>
+  <si>
+    <t>94500</t>
+  </si>
+  <si>
+    <t>94800</t>
+  </si>
+  <si>
+    <t>94020</t>
+  </si>
+  <si>
+    <t>94300</t>
+  </si>
+  <si>
+    <t>95050</t>
+  </si>
+  <si>
+    <t>94750</t>
+  </si>
+  <si>
+    <t>96150</t>
+  </si>
+  <si>
+    <t>96850</t>
+  </si>
+  <si>
+    <t>96805</t>
+  </si>
+  <si>
+    <t>97020</t>
+  </si>
+  <si>
+    <t>96900</t>
+  </si>
+  <si>
+    <t>98056</t>
+  </si>
+  <si>
+    <t>98150</t>
+  </si>
+  <si>
+    <t>98857</t>
+  </si>
+  <si>
+    <t>ROUTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1837,8 +2770,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1894,6 +2841,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
   </fills>
@@ -1953,7 +2906,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2091,8 +3044,13 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2449,22 +3407,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D39D926-E7A0-4D94-A6B9-A8D9A8B3E680}">
   <dimension ref="A2:K16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="24.6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="2" customWidth="1"/>
     <col min="5" max="5" width="15" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="38.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="44.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.5546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="42" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="12" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="68.45">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -2499,7 +3457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -2526,7 +3484,7 @@
       </c>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="4" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -2553,7 +3511,7 @@
       </c>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -2580,7 +3538,7 @@
       </c>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -2609,7 +3567,7 @@
       </c>
       <c r="K6" s="15"/>
     </row>
-    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -2638,7 +3596,7 @@
       </c>
       <c r="K7" s="15"/>
     </row>
-    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -2665,7 +3623,7 @@
       </c>
       <c r="K8" s="18"/>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -2694,7 +3652,7 @@
       </c>
       <c r="K9" s="15"/>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -2723,7 +3681,7 @@
       </c>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -2752,7 +3710,7 @@
       </c>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -2773,7 +3731,7 @@
       </c>
       <c r="K12" s="15"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I16" s="10" t="s">
         <v>12</v>
       </c>
@@ -2786,258 +3744,246 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A8250D7-37BD-4D62-A9F5-193381FD3734}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
         <v>445</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="53" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>519</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" t="s">
         <v>520</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" t="s">
         <v>521</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" t="s">
         <v>522</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" t="s">
         <v>523</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" t="s">
         <v>524</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>449</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" t="s">
         <v>499</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" t="s">
         <v>449</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" t="s">
         <v>506</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" t="s">
         <v>449</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" t="s">
         <v>506</v>
       </c>
-      <c r="G3" s="53"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="53" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>450</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" t="s">
         <v>510</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" t="s">
         <v>450</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" t="s">
         <v>507</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" t="s">
         <v>450</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" t="s">
         <v>507</v>
       </c>
-      <c r="G4" s="53"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="53" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>451</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" t="s">
         <v>464</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" t="s">
         <v>451</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" t="s">
         <v>508</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" t="s">
         <v>451</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" t="s">
         <v>508</v>
       </c>
-      <c r="G5" s="53"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="53" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>452</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" t="s">
         <v>465</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" t="s">
         <v>452</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" t="s">
         <v>509</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" t="s">
         <v>452</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" t="s">
         <v>488</v>
       </c>
-      <c r="G6" s="53"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="53" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>453</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" t="s">
         <v>512</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" t="s">
         <v>453</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" t="s">
         <v>455</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" t="s">
         <v>453</v>
       </c>
       <c r="F7" s="24" t="s">
         <v>499</v>
       </c>
-      <c r="G7" s="53"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="53" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>506</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53" t="s">
+      <c r="C8" t="s">
         <v>506</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" t="s">
         <v>466</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" t="s">
         <v>499</v>
       </c>
       <c r="F8" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="G8" s="53"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="53" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>507</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" t="s">
         <v>510</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" t="s">
         <v>507</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" t="s">
         <v>467</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" t="s">
         <v>506</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>501</v>
       </c>
-      <c r="G9" s="53"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="53" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>508</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53" t="s">
+      <c r="C10" t="s">
         <v>508</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" t="s">
         <v>513</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" t="s">
         <v>507</v>
       </c>
       <c r="F10" s="24" t="s">
         <v>502</v>
       </c>
-      <c r="G10" s="53"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="53" t="s">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>509</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>499</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" t="s">
         <v>454</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>499</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" t="s">
         <v>508</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>506</v>
       </c>
-      <c r="G11" s="53"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="53" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>455</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" t="s">
         <v>488</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" t="s">
         <v>510</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>507</v>
       </c>
-      <c r="G12" s="53"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="53" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>466</v>
       </c>
       <c r="B13" s="24" t="s">
@@ -3049,16 +3995,15 @@
       <c r="D13" s="24" t="s">
         <v>501</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" t="s">
         <v>465</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>508</v>
       </c>
-      <c r="G13" s="53"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="53" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>467</v>
       </c>
       <c r="B14" s="24" t="s">
@@ -3070,14 +4015,12 @@
       <c r="D14" s="24" t="s">
         <v>502</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E14" t="s">
         <v>512</v>
       </c>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="53" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>513</v>
       </c>
       <c r="B15" s="24" t="s">
@@ -3092,10 +4035,8 @@
       <c r="E15" s="24" t="s">
         <v>499</v>
       </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-    </row>
-    <row r="16" spans="1:7">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
         <v>499</v>
       </c>
@@ -3111,10 +4052,8 @@
       <c r="E16" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-    </row>
-    <row r="17" spans="1:5">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>500</v>
       </c>
@@ -3131,62 +4070,48 @@
         <v>501</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
         <v>501</v>
       </c>
-      <c r="B18" s="53"/>
       <c r="C18" s="24" t="s">
         <v>507</v>
       </c>
-      <c r="D18" s="53"/>
       <c r="E18" s="24" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
         <v>502</v>
       </c>
-      <c r="B19" s="53"/>
       <c r="C19" s="24" t="s">
         <v>508</v>
       </c>
-      <c r="D19" s="53"/>
       <c r="E19" s="24" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
         <v>506</v>
       </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
       <c r="E20" s="24" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>507</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
       <c r="E21" s="24" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
         <v>508</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3199,161 +4124,125 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D2F47F-936F-424A-96FD-34C50C33A88E}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>526</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53" t="s">
+      <c r="C1" t="s">
         <v>527</v>
       </c>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53" t="s">
+      <c r="E1" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="53" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>529</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53" t="s">
+      <c r="C2" t="s">
         <v>530</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53" t="s">
+      <c r="E2" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>532</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53" t="s">
+      <c r="C3" t="s">
         <v>533</v>
       </c>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53" t="s">
+      <c r="E3" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="53" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>535</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53" t="s">
+      <c r="C4" t="s">
         <v>536</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53" t="s">
+      <c r="E4" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="53" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>538</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53" t="s">
+      <c r="C5" t="s">
         <v>539</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53" t="s">
+      <c r="E5" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="53" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>541</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53" t="s">
+      <c r="C6" t="s">
         <v>542</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53" t="s">
+      <c r="E6" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="53" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>544</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53" t="s">
+      <c r="C7" t="s">
         <v>545</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53" t="s">
+      <c r="E7" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="53" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>547</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53" t="s">
+      <c r="C8" t="s">
         <v>548</v>
       </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="53" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>549</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53" t="s">
+      <c r="C9" t="s">
         <v>550</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="53" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>551</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="53" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>552</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="53" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>553</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="53" t="s">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>554</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3363,22 +4252,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEDE0C5-2A47-4471-88E7-341CFFF617B6}">
   <dimension ref="A2:K16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="24.6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="24.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" customWidth="1"/>
-    <col min="2" max="3" width="20.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="17" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="38.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="33.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="41.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="6" width="19.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="33.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="41.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="45.6">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="45.6" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -3413,7 +4302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -3448,7 +4337,7 @@
       </c>
       <c r="K3" s="15"/>
     </row>
-    <row r="4" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="4" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19">
         <v>2</v>
       </c>
@@ -3477,7 +4366,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -3506,7 +4395,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -3541,7 +4430,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="7" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -3578,7 +4467,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1">
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -3613,7 +4502,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="9" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -3648,7 +4537,7 @@
       </c>
       <c r="K9" s="15"/>
     </row>
-    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="10" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -3683,7 +4572,7 @@
       </c>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="11" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -3718,7 +4607,7 @@
       </c>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:11" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -3753,7 +4642,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1">
+    <row r="13" spans="1:11" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -3788,7 +4677,7 @@
       </c>
       <c r="K13" s="6"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I16" s="10" t="s">
         <v>12</v>
       </c>
@@ -3802,2892 +4691,3885 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB923D5B-1288-4E4B-A42D-1967DA205059}">
   <dimension ref="A1:F352"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="2" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.15" customHeight="1">
+    <row r="1" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-    </row>
-    <row r="2" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C1" s="53" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B2" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C2" s="54" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C3" s="54" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B4" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C4" s="54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B5" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C5" s="54" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B6" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C6" s="54" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B7" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C7" s="54" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B8" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-    </row>
-    <row r="9" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C8" s="54" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B9" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-    </row>
-    <row r="10" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C9" s="54" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B10" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C10" s="54" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C11" s="54" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C12" s="54" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B13" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C13" s="54" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B14" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53" t="s">
+      <c r="C14" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="F14" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16.899999999999999" customHeight="1">
+    <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.899999999999999" customHeight="1">
+      <c r="C15" s="54" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B16" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-    </row>
-    <row r="17" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C16" s="54" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="52" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C17" s="54" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="50" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C18" s="54" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B19" s="52" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C19" s="54" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="50" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C20" s="54" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B21" s="52" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C21" s="54" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B22" s="50" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C22" s="54" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B23" s="52" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C23" s="54" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B24" s="50" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C24" s="54" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B25" s="52" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C25" s="54" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B26" s="50" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C26" s="54" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B27" s="52" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C27" s="54" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B28" s="50" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C28" s="54" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B29" s="52" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C29" s="54" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
         <v>65</v>
       </c>
       <c r="B30" s="50" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C30" s="54" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="51" t="s">
         <v>65</v>
       </c>
       <c r="B31" s="52" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C31" s="54" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B32" s="50" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C32" s="54" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B33" s="52" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C33" s="54" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B34" s="50" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C34" s="54" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B35" s="52" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C35" s="54" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B36" s="50" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C36" s="54" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B37" s="52" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C37" s="54" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C38" s="54" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B39" s="52" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C39" s="54" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B40" s="50" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C40" s="54" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B41" s="52" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C41" s="54" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B42" s="50" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C42" s="54" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B43" s="52" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C43" s="54" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B44" s="50" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C44" s="54" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B45" s="52" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C45" s="54" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B46" s="50" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C46" s="54" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B47" s="52" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C47" s="54" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B48" s="50" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C48" s="54" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B49" s="52" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C49" s="54" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B50" s="50" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C50" s="54" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B51" s="52" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C51" s="54" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B52" s="50" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C52" s="54" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B53" s="52" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C53" s="54" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B54" s="50" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C54" s="54" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B55" s="52" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C55" s="54" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="49" t="s">
         <v>97</v>
       </c>
       <c r="B56" s="50" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C56" s="54" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="51" t="s">
         <v>97</v>
       </c>
       <c r="B57" s="52" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C57" s="54" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="49" t="s">
         <v>121</v>
       </c>
       <c r="B58" s="50" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C58" s="54" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="51" t="s">
         <v>121</v>
       </c>
       <c r="B59" s="52" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C59" s="54" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="49" t="s">
         <v>121</v>
       </c>
       <c r="B60" s="50" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C60" s="54" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="51" t="s">
         <v>121</v>
       </c>
       <c r="B61" s="52" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C61" s="54" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="49" t="s">
         <v>121</v>
       </c>
       <c r="B62" s="50" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C62" s="54" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="51" t="s">
         <v>121</v>
       </c>
       <c r="B63" s="52" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C63" s="54" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="49" t="s">
         <v>121</v>
       </c>
       <c r="B64" s="50" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C64" s="54" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="51" t="s">
         <v>121</v>
       </c>
       <c r="B65" s="52" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C65" s="54" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="49" t="s">
         <v>121</v>
       </c>
       <c r="B66" s="50" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C66" s="54" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="51" t="s">
         <v>121</v>
       </c>
       <c r="B67" s="52" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C67" s="54" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="49" t="s">
         <v>121</v>
       </c>
       <c r="B68" s="50" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C68" s="54" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="49" t="s">
         <v>133</v>
       </c>
       <c r="B69" s="50" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C69" s="54" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="51" t="s">
         <v>133</v>
       </c>
       <c r="B70" s="52" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C70" s="54" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="49" t="s">
         <v>133</v>
       </c>
       <c r="B71" s="50" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C71" s="54" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="51" t="s">
         <v>133</v>
       </c>
       <c r="B72" s="52" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C72" s="54" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="49" t="s">
         <v>133</v>
       </c>
       <c r="B73" s="50" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C73" s="54" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="51" t="s">
         <v>133</v>
       </c>
       <c r="B74" s="52" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C74" s="54" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="49" t="s">
         <v>133</v>
       </c>
       <c r="B75" s="50" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C75" s="54" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="51" t="s">
         <v>133</v>
       </c>
       <c r="B76" s="52" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C76" s="54" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B77" s="50" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C77" s="54" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B78" s="52" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C78" s="54" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B79" s="50" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C79" s="54" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B80" s="52" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C80" s="54" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B81" s="50" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C81" s="54" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B82" s="52" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C82" s="54" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B83" s="50" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C83" s="54" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B84" s="52" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C84" s="54" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B85" s="50" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C85" s="54" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B86" s="52" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C86" s="54" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B87" s="50" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C87" s="54" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B88" s="52" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C88" s="54" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B89" s="50" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C89" s="54" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B90" s="52" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C90" s="54" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B91" s="50" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C91" s="54" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B92" s="52" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C92" s="54" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B93" s="50" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C93" s="54" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B94" s="52" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C94" s="54" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B95" s="50" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C95" s="54" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B96" s="52" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C96" s="54" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B97" s="50" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C97" s="54" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B98" s="52" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C98" s="54" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B99" s="50" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C99" s="54" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B100" s="52" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C100" s="54" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B101" s="50" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C101" s="54" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B102" s="52" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C102" s="54" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B103" s="50" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C103" s="54" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B104" s="52" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C104" s="54" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B105" s="50" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C105" s="54" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="51" t="s">
         <v>142</v>
       </c>
       <c r="B106" s="52" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C106" s="54" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="49" t="s">
         <v>142</v>
       </c>
       <c r="B107" s="50" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C107" s="54" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B108" s="50" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C108" s="54" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B109" s="52" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C109" s="54" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B110" s="50" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C110" s="54" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B111" s="52" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C111" s="54" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B112" s="50" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C112" s="54" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B113" s="52" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C113" s="54" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B114" s="50" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C114" s="54" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B115" s="52" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C115" s="54" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B116" s="50" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C116" s="54" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B117" s="52" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C117" s="54" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B118" s="50" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C118" s="54" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B119" s="52" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C119" s="54" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B120" s="50" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C120" s="54" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B121" s="52" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C121" s="54" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B122" s="50" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C122" s="54" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B123" s="52" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C123" s="54" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B124" s="50" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C124" s="54" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B125" s="52" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C125" s="54" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B126" s="50" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C126" s="54" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B127" s="52" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C127" s="54" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B128" s="50" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C128" s="54" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B129" s="52" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C129" s="54" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B130" s="50" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C130" s="54" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B131" s="52" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C131" s="54" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B132" s="50" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C132" s="54" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B133" s="52" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C133" s="54" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B134" s="50" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C134" s="54" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B135" s="52" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C135" s="54" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="49" t="s">
         <v>174</v>
       </c>
       <c r="B136" s="50" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C136" s="54" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="51" t="s">
         <v>174</v>
       </c>
       <c r="B137" s="52" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C137" s="54" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B138" s="50" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C138" s="54" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B139" s="52" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C139" s="54" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B140" s="50" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C140" s="54" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B141" s="52" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C141" s="54" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B142" s="50" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C142" s="54" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B143" s="52" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C143" s="54" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B144" s="50" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C144" s="54" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B145" s="52" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C145" s="54" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B146" s="50" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C146" s="54" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B147" s="52" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C147" s="54" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B148" s="50" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C148" s="54" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B149" s="52" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C149" s="54" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B150" s="50" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C150" s="54" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B151" s="52" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C151" s="54" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B152" s="50" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C152" s="54" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B153" s="52" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C153" s="54" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B154" s="50" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C154" s="54" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B155" s="52" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C155" s="54" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B156" s="50" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C156" s="54" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B157" s="52" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C157" s="54" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B158" s="50" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C158" s="54" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B159" s="52" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C159" s="54" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B160" s="50" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C160" s="54" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B161" s="52" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C161" s="54" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B162" s="50" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C162" s="54" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B163" s="52" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C163" s="54" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B164" s="50" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C164" s="54" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B165" s="52" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C165" s="54" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B166" s="50" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C166" s="54" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="51" t="s">
         <v>205</v>
       </c>
       <c r="B167" s="52" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C167" s="54" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="49" t="s">
         <v>205</v>
       </c>
       <c r="B168" s="50" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C168" s="54" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B169" s="50" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C169" s="54" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B170" s="52" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C170" s="54" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B171" s="50" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C171" s="54" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B172" s="52" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="173" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C172" s="54" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B173" s="50" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C173" s="54" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B174" s="52" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C174" s="54" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B175" s="50" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C175" s="54" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B176" s="52" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C176" s="54" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B177" s="50" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C177" s="54" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B178" s="52" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C178" s="54" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B179" s="50" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C179" s="54" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B180" s="52" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C180" s="54" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B181" s="50" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C181" s="54" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B182" s="52" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C182" s="54" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="49" t="s">
         <v>237</v>
       </c>
       <c r="B183" s="50" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="184" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C183" s="54" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="51" t="s">
         <v>237</v>
       </c>
       <c r="B184" s="52" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="185" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C184" s="54" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B185" s="50" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="186" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C185" s="54" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B186" s="52" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="187" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C186" s="54" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B187" s="50" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="188" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C187" s="54" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B188" s="52" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="189" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C188" s="54" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B189" s="50" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="190" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C189" s="54" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B190" s="52" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="191" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C190" s="54" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B191" s="50" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="192" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C191" s="54" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B192" s="52" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="193" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C192" s="54" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B193" s="50" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="194" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C193" s="54" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B194" s="52" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="195" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C194" s="54" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B195" s="50" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="196" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C195" s="54" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B196" s="52" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="197" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C196" s="54" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B197" s="50" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="198" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C197" s="54" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B198" s="52" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="199" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C198" s="54" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B199" s="50" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C199" s="54" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="51" t="s">
         <v>254</v>
       </c>
       <c r="B200" s="52" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="201" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C200" s="54" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="49" t="s">
         <v>254</v>
       </c>
       <c r="B201" s="50" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="202" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C201" s="54" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B202" s="50" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C202" s="54" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B203" s="52" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="204" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C203" s="54" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B204" s="50" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="205" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C204" s="54" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B205" s="52" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="206" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C205" s="54" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B206" s="50" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="207" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C206" s="54" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B207" s="52" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="208" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C207" s="54" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B208" s="50" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="209" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C208" s="54" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B209" s="52" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="210" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C209" s="54" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B210" s="50" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="211" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C210" s="54" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B211" s="52" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="212" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C211" s="54" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B212" s="50" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="213" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C212" s="54" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B213" s="52" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="214" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C213" s="54" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B214" s="50" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="215" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C214" s="54" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B215" s="52" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="216" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C215" s="54" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B216" s="50" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="217" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C216" s="54" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B217" s="52" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="218" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C217" s="54" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B218" s="50" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="219" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C218" s="54" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B219" s="52" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="220" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C219" s="54" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="49" t="s">
         <v>272</v>
       </c>
       <c r="B220" s="50" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="221" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C220" s="54" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="51" t="s">
         <v>272</v>
       </c>
       <c r="B221" s="52" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="222" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C221" s="54" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="49" t="s">
         <v>293</v>
       </c>
       <c r="B222" s="50" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="223" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C222" s="54" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="51" t="s">
         <v>293</v>
       </c>
       <c r="B223" s="52" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="224" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C223" s="54" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="49" t="s">
         <v>293</v>
       </c>
       <c r="B224" s="50" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="225" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C224" s="54" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="51" t="s">
         <v>293</v>
       </c>
       <c r="B225" s="52" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="226" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C225" s="54" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="49" t="s">
         <v>293</v>
       </c>
       <c r="B226" s="50" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="227" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C226" s="54" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="51" t="s">
         <v>293</v>
       </c>
       <c r="B227" s="52" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="228" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C227" s="54" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="49" t="s">
         <v>293</v>
       </c>
       <c r="B228" s="50" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="229" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C228" s="54" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="51" t="s">
         <v>293</v>
       </c>
       <c r="B229" s="52" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="230" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C229" s="54" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="49" t="s">
         <v>293</v>
       </c>
       <c r="B230" s="50" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="231" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C230" s="54" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B231" s="50" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="232" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C231" s="54" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B232" s="52" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="233" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C232" s="54" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B233" s="50" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="234" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C233" s="54" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B234" s="52" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="235" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C234" s="54" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B235" s="50" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="236" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C235" s="54" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B236" s="52" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="237" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C236" s="54" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B237" s="50" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="238" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C237" s="54" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B238" s="52" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="239" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C238" s="54" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B239" s="50" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="240" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C239" s="54" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B240" s="52" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="241" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C240" s="54" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B241" s="50" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="242" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C241" s="54" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B242" s="52" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="243" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C242" s="54" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B243" s="50" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="244" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C243" s="54" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B244" s="52" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="245" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C244" s="54" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B245" s="50" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="246" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C245" s="54" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B246" s="52" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="247" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C246" s="54" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B247" s="50" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="248" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C247" s="54" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B248" s="52" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="249" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C248" s="54" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B249" s="50" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="250" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C249" s="54" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B250" s="52" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="251" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C250" s="54" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="49" t="s">
         <v>303</v>
       </c>
       <c r="B251" s="50" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="252" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C251" s="54" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B252" s="52" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="253" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C252" s="54" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B253" s="50" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="254" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C253" s="54" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B254" s="52" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="255" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C254" s="54" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B255" s="50" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="256" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C255" s="54" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B256" s="52" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="257" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C256" s="54" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B257" s="50" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="258" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C257" s="54" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B258" s="52" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="259" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C258" s="54" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B259" s="50" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="260" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C259" s="54" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B260" s="52" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="261" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C260" s="54" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B261" s="50" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="262" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C261" s="54" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B262" s="52" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="263" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C262" s="54" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B263" s="50" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="264" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C263" s="54" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B264" s="52" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="265" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C264" s="54" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B265" s="50" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="266" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C265" s="54" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B266" s="52" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="267" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C266" s="54" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B267" s="50" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="268" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C267" s="54" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B268" s="52" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="269" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C268" s="54" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B269" s="50" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="270" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C269" s="54" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="51" t="s">
         <v>325</v>
       </c>
       <c r="B270" s="52" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="271" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C270" s="54" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="49" t="s">
         <v>325</v>
       </c>
       <c r="B271" s="50" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="272" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C271" s="54" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B272" s="50" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="273" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C272" s="54" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B273" s="52" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="274" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C273" s="54" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B274" s="50" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="275" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C274" s="54" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B275" s="52" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="276" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C275" s="54" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B276" s="50" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="277" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C276" s="54" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B277" s="52" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="278" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C277" s="54" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B278" s="50" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="279" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C278" s="54" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B279" s="52" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="280" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C279" s="54" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B280" s="50" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="281" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C280" s="54" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B281" s="52" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="282" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C281" s="54" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B282" s="50" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="283" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C282" s="54" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B283" s="52" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="284" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C283" s="54" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B284" s="50" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="285" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C284" s="54" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B285" s="52" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="286" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C285" s="54" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="49" t="s">
         <v>344</v>
       </c>
       <c r="B286" s="50" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="287" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C286" s="54" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="51" t="s">
         <v>344</v>
       </c>
       <c r="B287" s="52" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="288" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C287" s="54" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B288" s="50" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="289" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C288" s="54" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B289" s="52" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="290" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C289" s="54" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B290" s="50" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="291" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C290" s="54" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B291" s="52" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="292" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C291" s="54" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B292" s="50" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="293" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C292" s="54" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B293" s="52" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="294" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C293" s="54" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B294" s="50" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="295" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C294" s="54" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B295" s="52" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="296" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C295" s="54" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B296" s="50" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="297" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C296" s="54" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B297" s="52" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="298" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C297" s="54" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B298" s="50" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="299" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C298" s="54" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B299" s="52" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="300" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C299" s="54" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B300" s="50" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="301" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C300" s="54" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B301" s="52" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="302" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C301" s="54" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B302" s="50" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="303" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C302" s="54" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B303" s="52" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="304" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C303" s="54" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B304" s="50" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="305" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C304" s="54" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B305" s="52" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="306" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C305" s="54" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B306" s="50" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="307" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C306" s="54" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B307" s="52" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="308" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C307" s="54" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B308" s="50" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="309" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C308" s="54" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B309" s="52" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="310" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C309" s="54" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B310" s="50" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="311" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C310" s="54" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B311" s="52" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="312" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C311" s="54" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B312" s="50" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="313" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C312" s="54" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B313" s="52" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="314" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C313" s="54" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B314" s="50" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="315" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C314" s="54" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B315" s="52" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="316" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C315" s="54" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B316" s="50" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="317" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C316" s="54" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="51" t="s">
         <v>361</v>
       </c>
       <c r="B317" s="52" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="318" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C317" s="54" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="49" t="s">
         <v>361</v>
       </c>
       <c r="B318" s="50" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="319" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C318" s="54" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B319" s="50" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="320" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C319" s="54" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B320" s="52" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="321" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C320" s="54" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B321" s="50" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="322" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C321" s="54" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B322" s="52" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="323" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C322" s="54" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B323" s="50" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="324" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C323" s="54" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B324" s="52" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="325" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C324" s="54" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B325" s="50" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="326" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C325" s="54" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B326" s="52" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="327" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C326" s="54" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B327" s="50" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="328" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C327" s="54" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B328" s="52" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="329" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C328" s="54" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B329" s="50" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="330" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C329" s="54" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B330" s="52" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="331" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C330" s="54" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B331" s="50" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="332" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C331" s="54" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B332" s="52" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="333" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C332" s="54" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B333" s="50" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="334" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C333" s="54" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B334" s="52" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="335" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C334" s="54" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B335" s="50" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="336" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C335" s="54" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B336" s="52" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="337" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C336" s="54" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B337" s="50" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="338" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C337" s="54" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B338" s="52" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="339" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C338" s="54" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B339" s="50" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="340" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C339" s="54" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B340" s="52" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="341" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C340" s="54" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B341" s="50" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="342" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C341" s="54" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B342" s="52" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="343" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C342" s="54" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B343" s="50" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="344" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C343" s="54" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B344" s="52" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="345" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C344" s="54" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B345" s="50" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="346" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C345" s="54" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B346" s="52" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="347" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C346" s="54" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B347" s="50" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="348" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C347" s="54" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B348" s="52" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="349" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C348" s="54" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B349" s="50" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="350" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C349" s="54" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B350" s="52" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="351" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C350" s="54" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="49" t="s">
         <v>393</v>
       </c>
       <c r="B351" s="50" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="352" spans="1:2" ht="16.899999999999999" customHeight="1">
+      <c r="C351" s="54" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="51" t="s">
         <v>393</v>
       </c>
       <c r="B352" s="52" t="s">
         <v>427</v>
+      </c>
+      <c r="C352" s="54" t="s">
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -6702,18 +8584,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="25"/>
+    <col min="6" max="6" width="28.88671875" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.9">
+    <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="30" t="s">
         <v>428</v>
       </c>
@@ -6733,7 +8615,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18">
+    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="32" t="s">
         <v>434</v>
       </c>
@@ -6753,7 +8635,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18">
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
         <v>434</v>
       </c>
@@ -6774,7 +8656,7 @@
         <v>14542.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18">
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
         <v>434</v>
       </c>
@@ -6795,7 +8677,7 @@
         <v>14311.5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18">
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
         <v>434</v>
       </c>
@@ -6816,7 +8698,7 @@
         <v>14689.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
         <v>434</v>
       </c>
@@ -6837,7 +8719,7 @@
         <v>13251</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="32" t="s">
         <v>434</v>
       </c>
@@ -6858,7 +8740,7 @@
         <v>10762.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
         <v>434</v>
       </c>
@@ -6879,7 +8761,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>434</v>
       </c>
@@ -6900,7 +8782,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
         <v>434</v>
       </c>
@@ -6921,7 +8803,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="32" t="s">
         <v>434</v>
       </c>
@@ -6942,7 +8824,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35" t="s">
         <v>436</v>
       </c>
@@ -6963,7 +8845,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="35" t="s">
         <v>436</v>
       </c>
@@ -6984,7 +8866,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>436</v>
       </c>
@@ -7005,7 +8887,7 @@
         <v>4231.5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
         <v>440</v>
       </c>
@@ -7026,7 +8908,7 @@
         <v>8494.5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="41" t="s">
         <v>442</v>
       </c>
@@ -7047,7 +8929,7 @@
         <v>13314</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="41" t="s">
         <v>442</v>
       </c>
@@ -7068,7 +8950,7 @@
         <v>8662.5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="41" t="s">
         <v>442</v>
       </c>
@@ -7089,7 +8971,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="44" t="s">
         <v>445</v>
       </c>
@@ -7110,7 +8992,7 @@
         <v>14164.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="44" t="s">
         <v>445</v>
       </c>
@@ -7131,7 +9013,7 @@
         <v>13723.5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="44" t="s">
         <v>445</v>
       </c>
@@ -7152,7 +9034,7 @@
         <v>13377</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="44" t="s">
         <v>445</v>
       </c>
@@ -7173,7 +9055,7 @@
         <v>10027.5</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="44" t="s">
         <v>445</v>
       </c>
@@ -7194,7 +9076,7 @@
         <v>10384.5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="44" t="s">
         <v>445</v>
       </c>
@@ -7215,7 +9097,7 @@
         <v>4620</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="44" t="s">
         <v>445</v>
       </c>
@@ -7236,7 +9118,7 @@
         <v>4368</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="44" t="s">
         <v>445</v>
       </c>
@@ -7257,7 +9139,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="44" t="s">
         <v>445</v>
       </c>
@@ -7278,98 +9160,98 @@
         <v>1144.5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="29"/>
     </row>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="29"/>
     </row>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="27"/>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
       <c r="E30" s="29"/>
     </row>
-    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="27"/>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
       <c r="E31" s="29"/>
     </row>
-    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="27"/>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
       <c r="E32" s="29"/>
     </row>
-    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="27"/>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
       <c r="E33" s="29"/>
     </row>
-    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="27"/>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
       <c r="E34" s="29"/>
     </row>
-    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="27"/>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
       <c r="E35" s="29"/>
     </row>
-    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="27"/>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
       <c r="E36" s="29"/>
     </row>
-    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="27"/>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
       <c r="E37" s="29"/>
     </row>
-    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="27"/>
       <c r="B38" s="28"/>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
       <c r="E38" s="29"/>
     </row>
-    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="27"/>
       <c r="B39" s="28"/>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
       <c r="E39" s="29"/>
     </row>
-    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1">
+    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27"/>
       <c r="B40" s="28"/>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
       <c r="E40" s="29"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E41" s="26"/>
     </row>
   </sheetData>
@@ -7381,768 +9263,768 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1DC0BE-3C08-4CFF-8806-21F8A4247F7D}">
   <dimension ref="A1:B95"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="75.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>446</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="53">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="53">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="53">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="53">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="53">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="53">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="53">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="53">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="53">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="53">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="53">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="53">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="53">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="53">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="53">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="53">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="53">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="53">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="53">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="53">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="53">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="53">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="53">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="53">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="53" t="s">
+      <c r="B25" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="53">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="53">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="53">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="53">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="53">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="53" t="s">
+      <c r="B30" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="53">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="53" t="s">
+      <c r="B31" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="53">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="53">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="53" t="s">
+      <c r="B33" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="53">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="53" t="s">
+      <c r="B34" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="53">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="53" t="s">
+      <c r="B35" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="53">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="53" t="s">
+      <c r="B36" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="53">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="53" t="s">
+      <c r="B37" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="53">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B38" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="53">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="53" t="s">
+      <c r="B39" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="53">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="53" t="s">
+      <c r="B40" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="53">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="53" t="s">
+      <c r="B41" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="53">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="53" t="s">
+      <c r="B42" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="53">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="53" t="s">
+      <c r="B43" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="53">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="53" t="s">
+      <c r="B44" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="53">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="53" t="s">
+      <c r="B45" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="53">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="53" t="s">
+      <c r="B46" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="53">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="53" t="s">
+      <c r="B47" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="53">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="53" t="s">
+      <c r="B48" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="53">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="53" t="s">
+      <c r="B49" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="53">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="53" t="s">
+      <c r="B50" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="53">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="53" t="s">
+      <c r="B51" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="53">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="53" t="s">
+      <c r="B52" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="53">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="53" t="s">
+      <c r="B53" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="53">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="53" t="s">
+      <c r="B54" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="53">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="53" t="s">
+      <c r="B55" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="53">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="53" t="s">
+      <c r="B56" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="53">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="53" t="s">
+      <c r="B57" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="53">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="53" t="s">
+      <c r="B58" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="53">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="53" t="s">
+      <c r="B59" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="53">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="53" t="s">
+      <c r="B60" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="53">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="53" t="s">
+      <c r="B61" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="53">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="53" t="s">
+      <c r="B62" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="53">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="53" t="s">
+      <c r="B63" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="53">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" s="53" t="s">
+      <c r="B64" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="53">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="53" t="s">
+      <c r="B65" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="53">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" s="53" t="s">
+      <c r="B66" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="53">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="53" t="s">
+      <c r="B67" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="53">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" s="53" t="s">
+      <c r="B68" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="53">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="53" t="s">
+      <c r="B69" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="53">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" s="53" t="s">
+      <c r="B70" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="53">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="53" t="s">
+      <c r="B71" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="53">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="53" t="s">
+      <c r="B72" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="53">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="53" t="s">
+      <c r="B73" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="53">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" s="53" t="s">
+      <c r="B74" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="53">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="53" t="s">
+      <c r="B75" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="53">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" s="53" t="s">
+      <c r="B76" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="53">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="53" t="s">
+      <c r="B77" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="53">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" s="53" t="s">
+      <c r="B78" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="53">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="53" t="s">
+      <c r="B79" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="53">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="53" t="s">
+      <c r="B80" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="53">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="53" t="s">
+      <c r="B81" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="53">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" s="53" t="s">
+      <c r="B82" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="53">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="53" t="s">
+      <c r="B83" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="53">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" s="53" t="s">
+      <c r="B84" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="53">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="53" t="s">
+      <c r="B85" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="53">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" s="53" t="s">
+      <c r="B86" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="53">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="53" t="s">
+      <c r="B87" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="53">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" s="53" t="s">
+      <c r="B88" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="53">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="53" t="s">
+      <c r="B89" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="53">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" s="53" t="s">
+      <c r="B90" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="53">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="53" t="s">
+      <c r="B91" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="53">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" s="53" t="s">
+      <c r="B92" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="53">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="53" t="s">
+      <c r="B93" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="53">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" s="53" t="s">
+      <c r="B94" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="53">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="53" t="s">
+      <c r="B95" t="s">
         <v>514</v>
       </c>
     </row>
@@ -8158,239 +10040,243 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376B93B6-7CD8-4B1C-BCCE-53C84FB0C94C}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="75.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>515</v>
       </c>
-      <c r="B1" s="53"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="53">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>25</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="53">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>26</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="53">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>27</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="53">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>28</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="53">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>29</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="53">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>30</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="53">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>31</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="53">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>32</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="53">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>37</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="53">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>39</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="53">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>40</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="53">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>41</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="53">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>45</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="53">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>60</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="53">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>61</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="53">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>66</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="53">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>67</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="53">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>69</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="53">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>70</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="53">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>71</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="53">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>72</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="53">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>73</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="53">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>74</v>
       </c>
-      <c r="B25" s="53" t="s">
+      <c r="B25" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="53">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>75</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="53">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>76</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="53">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>77</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="53">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>84</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="53">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>85</v>
       </c>
-      <c r="B30" s="53" t="s">
+      <c r="B30" t="s">
         <v>505</v>
       </c>
     </row>
@@ -8402,222 +10288,226 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E29A849C-0396-4A45-9316-83F0776D4FED}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="68" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>516</v>
       </c>
-      <c r="B1" s="53"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="53">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="53">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="53">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="53">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="53">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="53">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>23</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="53">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>24</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="53">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>33</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="53">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>34</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="53">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>35</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="53">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>36</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="53">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>68</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="53">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>78</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="53">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>79</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="53">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>80</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="53">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>81</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="53">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>82</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="53">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>83</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="53">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>86</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="53">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>87</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="53">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>88</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="53">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>89</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="53">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>90</v>
       </c>
-      <c r="B25" s="53" t="s">
+      <c r="B25" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="53">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>92</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="53">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>93</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="53">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>94</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" t="s">
         <v>514</v>
       </c>
     </row>
@@ -8629,136 +10519,134 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7476908D-3A9A-4301-9740-379B31A7722E}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>517</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="53">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>64</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" t="s">
         <v>518</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="53">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>58</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" t="s">
         <v>518</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="53">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>62</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" t="s">
         <v>518</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="53">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>63</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" t="s">
         <v>518</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="53">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>91</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" t="s">
         <v>518</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="53">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>54</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" t="s">
         <v>518</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="53">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>57</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" t="s">
         <v>518</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="53">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>59</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" t="s">
         <v>518</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="53">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>56</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" t="s">
         <v>518</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="53">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>55</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" t="s">
         <v>518</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="53">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>65</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" t="s">
         <v>518</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" t="s">
         <v>485</v>
       </c>
     </row>
@@ -8770,442 +10658,402 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC53B66-DA17-482E-B0A4-0607724DBC4A}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="75.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="73.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="75.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="53" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>519</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" t="s">
         <v>520</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" t="s">
         <v>521</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" t="s">
         <v>522</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" t="s">
         <v>523</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" t="s">
         <v>524</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>456</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" t="s">
         <v>459</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" t="s">
         <v>456</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" t="s">
         <v>463</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" t="s">
         <v>456</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" t="s">
         <v>463</v>
       </c>
-      <c r="G3" s="53"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="53" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>457</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" t="s">
         <v>461</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" t="s">
         <v>457</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" t="s">
         <v>468</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" t="s">
         <v>457</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" t="s">
         <v>473</v>
       </c>
-      <c r="G4" s="53"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="53" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>458</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" t="s">
         <v>462</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" t="s">
         <v>458</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" t="s">
         <v>473</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" t="s">
         <v>458</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" t="s">
         <v>489</v>
       </c>
-      <c r="G5" s="53"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="53" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>459</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" t="s">
         <v>463</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" t="s">
         <v>460</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" t="s">
         <v>489</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" t="s">
         <v>463</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" t="s">
         <v>490</v>
       </c>
-      <c r="G6" s="53"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="53" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>461</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" t="s">
         <v>470</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" t="s">
         <v>463</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" t="s">
         <v>490</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" t="s">
         <v>473</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" t="s">
         <v>491</v>
       </c>
-      <c r="G7" s="53"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="53" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>462</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" t="s">
         <v>472</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" t="s">
         <v>471</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" t="s">
         <v>491</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" t="s">
         <v>489</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" t="s">
         <v>492</v>
       </c>
-      <c r="G8" s="53"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="53" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>463</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" t="s">
         <v>473</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" t="s">
         <v>473</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" t="s">
         <v>492</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" t="s">
         <v>490</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" t="s">
         <v>493</v>
       </c>
-      <c r="G9" s="53"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="53" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>470</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" t="s">
         <v>480</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" t="s">
         <v>489</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" t="s">
         <v>493</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" t="s">
         <v>491</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" t="s">
         <v>494</v>
       </c>
-      <c r="G10" s="53"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="53" t="s">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>472</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" t="s">
         <v>481</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" t="s">
         <v>490</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" t="s">
         <v>494</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" t="s">
         <v>492</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" t="s">
         <v>495</v>
       </c>
-      <c r="G11" s="53"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="53" t="s">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>473</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" t="s">
         <v>487</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" t="s">
         <v>491</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" t="s">
         <v>495</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" t="s">
         <v>493</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" t="s">
         <v>496</v>
       </c>
-      <c r="G12" s="53"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="53" t="s">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>480</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" t="s">
         <v>489</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" t="s">
         <v>492</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" t="s">
         <v>496</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" t="s">
         <v>494</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" t="s">
         <v>497</v>
       </c>
-      <c r="G13" s="53"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="53" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>481</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" t="s">
         <v>490</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" t="s">
         <v>493</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" t="s">
         <v>497</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E14" t="s">
         <v>496</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" t="s">
         <v>504</v>
       </c>
-      <c r="G14" s="53"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="53" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>486</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" t="s">
         <v>491</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" t="s">
         <v>494</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" t="s">
         <v>504</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" t="s">
         <v>497</v>
       </c>
-      <c r="F15" s="53" t="s">
+      <c r="F15" t="s">
         <v>505</v>
       </c>
-      <c r="G15" s="53"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="53" t="s">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>489</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" t="s">
         <v>496</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" t="s">
         <v>505</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" t="s">
         <v>504</v>
       </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="53" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>490</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" t="s">
         <v>493</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" t="s">
         <v>497</v>
       </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53" t="s">
+      <c r="E17" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="53" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>491</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" t="s">
         <v>494</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" t="s">
         <v>504</v>
       </c>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="53" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>492</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" t="s">
         <v>495</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" t="s">
         <v>505</v>
       </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="53" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>493</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" t="s">
         <v>496</v>
       </c>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="53" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>494</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" t="s">
         <v>497</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="53" t="s">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>496</v>
       </c>
-      <c r="B22" s="53" t="s">
+      <c r="B22" t="s">
         <v>504</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="53" t="s">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>497</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" t="s">
         <v>505</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="53" t="s">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>504</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="53" t="s">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>505</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
